--- a/BIM_TK_PowerBI_DataModel_2026.xlsx
+++ b/BIM_TK_PowerBI_DataModel_2026.xlsx
@@ -20280,7 +20280,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tài liệu tập hợp các lỗi hay gặp trong thiết kế HVAC các hạng mục</t>
+          <t>Tài liệu tập hợp các lỗi hay gặp trong thiết kế Kết cấu các hạng mục</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -20313,7 +20313,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Lưu ý: Bản gốc ghi nhầm 'HVAC', cần đổi thành 'Kết cấu'</t>
+          <t>Bình thường</t>
         </is>
       </c>
     </row>

--- a/BIM_TK_PowerBI_DataModel_2026.xlsx
+++ b/BIM_TK_PowerBI_DataModel_2026.xlsx
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (BIM Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Khuyết nhân sự chủ chốt</t>
+          <t>Đang làm việc</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Chưa tuyển đủ</t>
+          <t>KS Triển khai HVAC</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -11115,7 +11115,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -12519,7 +12519,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -13455,7 +13455,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -13923,7 +13923,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -14859,7 +14859,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -15327,7 +15327,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -15795,7 +15795,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -16263,7 +16263,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -17199,7 +17199,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -17667,7 +17667,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -18135,7 +18135,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Vị trí chờ tuyển (Hạ tầng)</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">

--- a/BIM_TK_PowerBI_DataModel_2026.xlsx
+++ b/BIM_TK_PowerBI_DataModel_2026.xlsx
@@ -678,12 +678,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ty Le Hoan Thanh Du An = DIVIDE(CALCULATE(COUNTROWS('07_Fact_BaoCaoCongViec'), '07_Fact_BaoCaoCongViec'[TinhTrang] = "Đã hoàn thành", '07_Fact_BaoCaoCongViec'[NhomCongViec] = "Dự án Thi công"), CALCULATE(COUNTROWS('07_Fact_BaoCaoCongViec'), '07_Fact_BaoCaoCongViec'[NhomCongViec] = "Dự án Thi công"), 0)</t>
+          <t>Ty Le Hoan Thanh Du An = DIVIDE(CALCULATE(COUNTROWS('07_Fact_BaoCaoCongViec'), '07_Fact_BaoCaoCongViec'[TinhTrang] = "Đã hoàn thành", '07_Fact_BaoCaoCongViec'[NhomCongViec] = "Dự án Mẫu (Thi công &amp; Triển khai)"), CALCULATE(COUNTROWS('07_Fact_BaoCaoCongViec'), '07_Fact_BaoCaoCongViec'[NhomCongViec] = "Dự án Mẫu (Thi công &amp; Triển khai)"), 0)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Gauge Chart tiến độ 7 dự án</t>
+          <t>Gauge Chart tiến độ 7 dự án mẫu</t>
         </is>
       </c>
     </row>
@@ -30715,12 +30715,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dự án Mega</t>
+          <t>Dự án Mẫu 01 (Mega)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -30767,12 +30767,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dự án Mega</t>
+          <t>Dự án Mẫu 01 (Mega)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -30819,12 +30819,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dự án Mega</t>
+          <t>Dự án Mẫu 01 (Mega)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -30871,12 +30871,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dự án Mega</t>
+          <t>Dự án Mẫu 01 (Mega)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -30923,12 +30923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dự án Mega</t>
+          <t>Dự án Mẫu 01 (Mega)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -30975,12 +30975,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dự án Mega</t>
+          <t>Dự án Mẫu 01 (Mega)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -31027,12 +31027,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dự án Mega</t>
+          <t>Dự án Mẫu 01 (Mega)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -31079,12 +31079,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dự án Mega</t>
+          <t>Dự án Mẫu 01 (Mega)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -31131,12 +31131,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dự án Mega</t>
+          <t>Dự án Mẫu 01 (Mega)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -31183,12 +31183,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dự án Mega</t>
+          <t>Dự án Mẫu 01 (Mega)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -31235,12 +31235,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dự án Mega</t>
+          <t>Dự án Mẫu 01 (Mega)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -31287,12 +31287,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dự án Mega</t>
+          <t>Dự án Mẫu 01 (Mega)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -31339,12 +31339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dự án Mega</t>
+          <t>Dự án Mẫu 01 (Mega)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -31391,12 +31391,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dự án Mega</t>
+          <t>Dự án Mẫu 01 (Mega)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -31443,12 +31443,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dự án Mega</t>
+          <t>Dự án Mẫu 01 (Mega)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dự án Mega</t>
+          <t>Dự án Mẫu 01 (Mega)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -31547,12 +31547,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dự án Mega</t>
+          <t>Dự án Mẫu 01 (Mega)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -31599,12 +31599,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dự án Mega</t>
+          <t>Dự án Mẫu 01 (Mega)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -31651,12 +31651,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dự án Mega</t>
+          <t>Dự án Mẫu 01 (Mega)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -31703,12 +31703,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dự án Mega</t>
+          <t>Dự án Mẫu 01 (Mega)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -31755,12 +31755,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dự án Mega</t>
+          <t>Dự án Mẫu 01 (Mega)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -31807,12 +31807,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dự án Mega</t>
+          <t>Dự án Mẫu 01 (Mega)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -31859,12 +31859,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dự án Mega</t>
+          <t>Dự án Mẫu 01 (Mega)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -31907,12 +31907,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dự án Mega</t>
+          <t>Dự án Mẫu 01 (Mega)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -31951,12 +31951,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dự án CasaFlora2</t>
+          <t>Dự án Mẫu 04 (CasaFlora2)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -32003,12 +32003,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dự án CasaFlora2</t>
+          <t>Dự án Mẫu 04 (CasaFlora2)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -32055,12 +32055,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dự án CasaFlora2</t>
+          <t>Dự án Mẫu 04 (CasaFlora2)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -32107,12 +32107,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dự án CasaFlora2</t>
+          <t>Dự án Mẫu 04 (CasaFlora2)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -32159,12 +32159,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dự án CasaFlora2</t>
+          <t>Dự án Mẫu 04 (CasaFlora2)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -32211,12 +32211,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dự án CasaFlora2</t>
+          <t>Dự án Mẫu 04 (CasaFlora2)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -32263,12 +32263,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dự án CasaFlora2</t>
+          <t>Dự án Mẫu 04 (CasaFlora2)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -32315,12 +32315,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dự án CasaFlora2</t>
+          <t>Dự án Mẫu 04 (CasaFlora2)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -32367,12 +32367,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dự án CasaFlora2</t>
+          <t>Dự án Mẫu 04 (CasaFlora2)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -32419,12 +32419,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dự án CasaFlora2</t>
+          <t>Dự án Mẫu 04 (CasaFlora2)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -32471,12 +32471,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dự án CasaFlora2</t>
+          <t>Dự án Mẫu 04 (CasaFlora2)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -32523,12 +32523,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dự án CasaFlora2</t>
+          <t>Dự án Mẫu 04 (CasaFlora2)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -32575,12 +32575,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dự án Kim Tín giai đoạn 3</t>
+          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -32627,12 +32627,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dự án Kim Tín giai đoạn 3</t>
+          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -32679,12 +32679,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dự án Kim Tín giai đoạn 3</t>
+          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -32731,12 +32731,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dự án Kim Tín giai đoạn 3</t>
+          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -32783,12 +32783,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dự án Kim Tín giai đoạn 3</t>
+          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -32831,12 +32831,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dự án Kim Tín giai đoạn 3</t>
+          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -32875,12 +32875,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dự án Kim Tín giai đoạn 3</t>
+          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -32927,12 +32927,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dự án Kim Tín giai đoạn 3</t>
+          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -32975,12 +32975,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dự án Kim Tín giai đoạn 3</t>
+          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -33027,12 +33027,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dự án Kim Tín giai đoạn 3</t>
+          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -33079,12 +33079,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dự án Kim Tín giai đoạn 3</t>
+          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -33127,12 +33127,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dự án Kim Tín giai đoạn 3</t>
+          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -33179,12 +33179,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dự án Kim Tín giai đoạn 3</t>
+          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -33231,12 +33231,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dự án Kim Tín giai đoạn 3</t>
+          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -33279,12 +33279,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dự án Kim Tín giai đoạn 3</t>
+          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -33331,12 +33331,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dự án Kim Tín giai đoạn 3</t>
+          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -33379,12 +33379,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dự án Kim Tín giai đoạn 3</t>
+          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -33431,12 +33431,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dự án Kim Tín giai đoạn 3</t>
+          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -33483,12 +33483,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dự án APF</t>
+          <t>Dự án Mẫu 03 (APF)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -33535,12 +33535,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dự án APF</t>
+          <t>Dự án Mẫu 03 (APF)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -33587,12 +33587,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dự án APF</t>
+          <t>Dự án Mẫu 03 (APF)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -33631,12 +33631,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dự án APF</t>
+          <t>Dự án Mẫu 03 (APF)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -33683,12 +33683,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dự án APF</t>
+          <t>Dự án Mẫu 03 (APF)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -33735,12 +33735,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dự án APF</t>
+          <t>Dự án Mẫu 03 (APF)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -33787,12 +33787,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dự án APF</t>
+          <t>Dự án Mẫu 03 (APF)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -33835,12 +33835,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dự án APF</t>
+          <t>Dự án Mẫu 03 (APF)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -33879,12 +33879,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dự án APF</t>
+          <t>Dự án Mẫu 03 (APF)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -33923,12 +33923,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dự án APF</t>
+          <t>Dự án Mẫu 03 (APF)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -33967,12 +33967,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dự án APF</t>
+          <t>Dự án Mẫu 03 (APF)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -34011,12 +34011,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dự án APF</t>
+          <t>Dự án Mẫu 03 (APF)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -34055,12 +34055,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dự án APF</t>
+          <t>Dự án Mẫu 03 (APF)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -34099,12 +34099,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dự án APF</t>
+          <t>Dự án Mẫu 03 (APF)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -34143,12 +34143,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dự án APF</t>
+          <t>Dự án Mẫu 03 (APF)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -34187,12 +34187,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dự án Suncasa</t>
+          <t>Dự án Mẫu 05 (Suncasa)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -34239,12 +34239,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dự án Suncasa</t>
+          <t>Dự án Mẫu 05 (Suncasa)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -34291,12 +34291,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dự án Suncasa</t>
+          <t>Dự án Mẫu 05 (Suncasa)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -34343,12 +34343,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dự án Suncasa</t>
+          <t>Dự án Mẫu 05 (Suncasa)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -34395,12 +34395,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dự án Suncasa</t>
+          <t>Dự án Mẫu 05 (Suncasa)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -34447,12 +34447,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dự án Suncasa</t>
+          <t>Dự án Mẫu 05 (Suncasa)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -34499,12 +34499,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dự án Suncasa</t>
+          <t>Dự án Mẫu 05 (Suncasa)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -34551,12 +34551,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dự án Suncasa</t>
+          <t>Dự án Mẫu 05 (Suncasa)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -34599,12 +34599,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dự án Suncasa</t>
+          <t>Dự án Mẫu 05 (Suncasa)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dự án các trạm Phú Quốc</t>
+          <t>Dự án Mẫu 06 (Phú Quốc)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -34699,12 +34699,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dự án các trạm Phú Quốc</t>
+          <t>Dự án Mẫu 06 (Phú Quốc)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -34751,12 +34751,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dự án các trạm Phú Quốc</t>
+          <t>Dự án Mẫu 06 (Phú Quốc)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -34803,12 +34803,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dự án các trạm Phú Quốc</t>
+          <t>Dự án Mẫu 06 (Phú Quốc)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -34855,12 +34855,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dự án các trạm Phú Quốc</t>
+          <t>Dự án Mẫu 06 (Phú Quốc)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -34907,12 +34907,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dự án các trạm Phú Quốc</t>
+          <t>Dự án Mẫu 06 (Phú Quốc)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -34959,12 +34959,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dự án các trạm Phú Quốc</t>
+          <t>Dự án Mẫu 06 (Phú Quốc)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -35011,12 +35011,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dự án BB052</t>
+          <t>Dự án Mẫu 07 (BB052)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -35063,12 +35063,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Dự án Thi công</t>
+          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dự án BB052</t>
+          <t>Dự án Mẫu 07 (BB052)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">

--- a/BIM_TK_PowerBI_DataModel_2026.xlsx
+++ b/BIM_TK_PowerBI_DataModel_2026.xlsx
@@ -30720,7 +30720,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 01 (Mega)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -30772,7 +30772,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 01 (Mega)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -30824,7 +30824,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 01 (Mega)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -30876,7 +30876,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 01 (Mega)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -30928,7 +30928,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 01 (Mega)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -30980,7 +30980,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 01 (Mega)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -31032,7 +31032,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 01 (Mega)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -31084,7 +31084,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 01 (Mega)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -31136,7 +31136,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 01 (Mega)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -31188,7 +31188,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 01 (Mega)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -31240,7 +31240,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 01 (Mega)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -31292,7 +31292,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 01 (Mega)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -31344,7 +31344,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 01 (Mega)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -31396,7 +31396,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 01 (Mega)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -31448,7 +31448,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 01 (Mega)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -31500,7 +31500,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 01 (Mega)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -31552,7 +31552,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 01 (Mega)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -31604,7 +31604,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 01 (Mega)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -31656,7 +31656,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 01 (Mega)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -31708,7 +31708,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 01 (Mega)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -31760,7 +31760,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 01 (Mega)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -31812,7 +31812,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 01 (Mega)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 01 (Mega)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -31912,7 +31912,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 01 (Mega)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -31956,7 +31956,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 04 (CasaFlora2)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -32008,7 +32008,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 04 (CasaFlora2)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -32060,7 +32060,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 04 (CasaFlora2)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -32112,7 +32112,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 04 (CasaFlora2)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -32164,7 +32164,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 04 (CasaFlora2)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -32216,7 +32216,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 04 (CasaFlora2)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -32268,7 +32268,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 04 (CasaFlora2)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -32320,7 +32320,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 04 (CasaFlora2)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -32372,7 +32372,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 04 (CasaFlora2)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 04 (CasaFlora2)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -32476,7 +32476,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 04 (CasaFlora2)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -32528,7 +32528,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 04 (CasaFlora2)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -32580,7 +32580,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -32632,7 +32632,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -32736,7 +32736,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -32788,7 +32788,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -32836,7 +32836,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -32880,7 +32880,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -32932,7 +32932,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -32980,7 +32980,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -33032,7 +33032,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -33084,7 +33084,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -33132,7 +33132,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -33184,7 +33184,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -33236,7 +33236,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -33284,7 +33284,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -33336,7 +33336,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -33384,7 +33384,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -33436,7 +33436,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 02 (Kim Tín GĐ3)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -33488,7 +33488,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 03 (APF)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -33540,7 +33540,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 03 (APF)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -33592,7 +33592,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 03 (APF)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -33636,7 +33636,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 03 (APF)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -33688,7 +33688,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 03 (APF)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -33740,7 +33740,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 03 (APF)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -33792,7 +33792,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 03 (APF)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -33840,7 +33840,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 03 (APF)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -33884,7 +33884,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 03 (APF)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -33928,7 +33928,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 03 (APF)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -33972,7 +33972,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 03 (APF)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -34016,7 +34016,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 03 (APF)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -34060,7 +34060,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 03 (APF)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 03 (APF)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -34148,7 +34148,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 03 (APF)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -34192,7 +34192,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 05 (Suncasa)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 05 (Suncasa)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -34296,7 +34296,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 05 (Suncasa)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -34348,7 +34348,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 05 (Suncasa)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -34400,7 +34400,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 05 (Suncasa)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -34452,7 +34452,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 05 (Suncasa)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -34504,7 +34504,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 05 (Suncasa)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -34556,7 +34556,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 05 (Suncasa)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -34604,7 +34604,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 05 (Suncasa)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -34652,7 +34652,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 06 (Phú Quốc)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -34704,7 +34704,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 06 (Phú Quốc)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -34756,7 +34756,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 06 (Phú Quốc)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -34808,7 +34808,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 06 (Phú Quốc)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -34860,7 +34860,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 06 (Phú Quốc)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -34912,7 +34912,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 06 (Phú Quốc)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -34964,7 +34964,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 06 (Phú Quốc)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -35016,7 +35016,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 07 (BB052)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -35068,7 +35068,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dự án Mẫu 07 (BB052)</t>
+          <t>Dự án Mẫu</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">

--- a/BIM_TK_PowerBI_DataModel_2026.xlsx
+++ b/BIM_TK_PowerBI_DataModel_2026.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Gauge Chart tiến độ 7 dự án mẫu</t>
+          <t>Gauge Chart tiến độ Dự Án Mẫu</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Quản lý thiết kế các dự án thuê ngoài chuẩn hóa theo yêu cầu nội bộ</t>
+          <t>Quản lý chuẩn hóa hồ sơ thiết kế chuyển đổi sang mô hình BIM nội bộ</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tỷ lệ dự án thuê ngoài tuân thủ chuẩn nội bộ</t>
+          <t>Tỷ lệ dự án thiết kế tuân thủ chuẩn BIM nội bộ</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1416,7 +1416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Quản lý chung</t>
+          <t>Quản lý điều hành</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TBP BIM - Thiết kế</t>
+          <t>Trưởng bộ phận BIM - Thiết kế</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,34 +1534,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GRP_BIM_XD</t>
+          <t>GRP_TK_BIM_KC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BIM Xây dựng (KT - KC)</t>
+          <t>Thiết kế &amp; BIM Kết cấu</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Trưởng nhóm BIM XD</t>
+          <t>Lead Bộ môn Kết cấu</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Nhân sự D (Lead Kết Cấu)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Leader</t>
+          <t>Lead Bộ Môn</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -1584,22 +1584,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GRP_BIM_XD</t>
+          <t>GRP_TK_BIM_KC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BIM Xây dựng (KT - KC)</t>
+          <t>Thiết kế &amp; BIM Kết cấu</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kỹ sư BIM KT - KC</t>
+          <t>Kỹ sư TK Kết cấu &amp; Kỹ sư BIM KC</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Nhân sự H, Nhân sự I, Nhân sự J, Nhân sự K...</t>
+          <t>KS Triển khai KC &amp; 3 KS BIM KC (Nhân sự J, K...)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1608,53 +1608,53 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Đã chia đều 3 KS BIM về bộ môn</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Biến động T04/2026 &amp; Cần tuyển thêm</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.7143</v>
+        <v>0.8333</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GRP_BIM_MEPF</t>
+          <t>GRP_TK_BIM_KT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BIM MEPF</t>
+          <t>Thiết kế &amp; BIM Kiến trúc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Trưởng nhóm BIM MEPF</t>
+          <t>Lead Bộ môn Kiến trúc</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Nhân sự E</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leader</t>
+          <t>Lead Bộ Môn</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1684,22 +1684,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GRP_BIM_MEPF</t>
+          <t>GRP_TK_BIM_KT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BIM MEPF</t>
+          <t>Thiết kế &amp; BIM Kiến trúc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kỹ sư BIM MEPF</t>
+          <t>KTS Triển khai &amp; Kỹ sư BIM Kiến trúc</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Nhân sự L &amp; KS BIM MEPF</t>
+          <t>KTS Triển khai &amp; 3 KS BIM KT (Nhân sự H, I...)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1708,121 +1708,121 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Đã chia đều 3 KS BIM về bộ môn</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
         <v>2</v>
       </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Đang làm việc</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GRP_BIM_HT</t>
+          <t>GRP_TK_BIM_MEP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BIM Hạ tầng</t>
+          <t>Thiết kế &amp; BIM Cơ điện (MEPF)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kỹ sư BIM Hạ tầng</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Nhân sự C (Lead BIM MEPF)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nhân viên</t>
+          <t>Lead Bộ Môn</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>2</v>
       </c>
       <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Đang làm việc</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Đang làm việc</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GRP_TK_KT</t>
+          <t>GRP_TK_BIM_MEP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Thiết kế Kiến trúc</t>
+          <t>Thiết kế &amp; BIM Cơ điện (MEPF)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chủ trì TK Kiến trúc</t>
+          <t>Kỹ sư TK Cơ Điện &amp; Kỹ sư BIM MEP</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Nhân sự E</t>
+          <t>KS Cơ Điện &amp; 3 KS BIM MEP (Nhân sự L &amp; KS MEP)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chủ trì</t>
+          <t>Nhân viên</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Đã đủ chủ trì</t>
+          <t>Đã chia đều 3 KS BIM về bộ môn</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1834,27 +1834,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GRP_TK_KT</t>
+          <t>GRP_TK_BIM_HVAC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Thiết kế Kiến trúc</t>
+          <t>Thiết kế &amp; BIM HVAC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kiến trúc sư triển khai</t>
+          <t>Lead Bộ môn HVAC</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KTS Triển khai</t>
+          <t>Nhân sự G</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nhân viên</t>
+          <t>Lead Bộ Môn</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1884,31 +1884,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GRP_TK_KC</t>
+          <t>GRP_TK_BIM_HVAC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Thiết kế Kết cấu</t>
+          <t>Thiết kế &amp; BIM HVAC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chủ trì TK Kết cấu</t>
+          <t>Kỹ sư TK HVAC &amp; Triển khai</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Nhân sự D</t>
+          <t>KS Triển khai HVAC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Chủ trì</t>
+          <t>Nhân viên</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -1918,50 +1918,50 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Đã đủ chủ trì</t>
+          <t>Đang làm việc</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRP_TK_KC</t>
+          <t>GRP_BIM_HT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Thiết kế Kết cấu</t>
+          <t>BIM Hạ tầng &amp; CDE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kỹ sư TK Kết cấu</t>
+          <t>Lead BIM Hạ tầng &amp; Quản trị CDE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>KS Triển khai KC</t>
+          <t>Nhân sự M</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nhân viên</t>
+          <t>Lead Bộ Môn</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1972,213 +1972,63 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GRP_TK_ME</t>
+          <t>GRP_BIM_HT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Thiết kế Điện - Cơ (CTN, PCCC)</t>
+          <t>BIM Hạ tầng &amp; CDE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chủ trì TK Điện - Cơ</t>
+          <t>Kỹ sư BIM Hạ tầng &amp; CDE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>2 KS BIM Hạ tầng &amp; CDE (Điều phối chia đều sang)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chủ trì</t>
+          <t>Nhân viên</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" t="n">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Đã chia đều 2 KS BIM về bộ môn</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Đã đủ chủ trì</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
       <c r="L12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>GRP_TK_ME</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Thiết kế Điện - Cơ (CTN, PCCC)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Kỹ sư TK Cơ - Điện</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>KS Triển khai Cơ - Điện</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Nhân viên</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Đang làm việc</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>GRP_TK_HVAC</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Thiết kế HVAC</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Chủ trì TK HVAC</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Nhân sự G</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Chủ trì</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Đã đủ chủ trì</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>GRP_TK_HVAC</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Thiết kế HVAC</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Kỹ sư TK HVAC</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>KS Triển khai HVAC</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Nhân viên</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Đang làm việc</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
     </row>
   </sheetData>
@@ -19071,7 +18921,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>ChuTriPhuTrach</t>
+          <t>LeadPhuTrach</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -30715,17 +30565,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D phần ngầm phục vụ phối hợp va chạm trạm nước thải2.1a-BP16.1a (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
+          <t>Triển khai mô hình 3D phần ngầm phục vụ phối hợp va chạm trạm xử lý nước thải (Dự Án Mẫu) (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -30767,17 +30617,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ đà kiềng trạm nước thải 2.1a-BP16.1a</t>
+          <t>Triển khai bản vẽ đà kiềng trạm xử lý nước thải (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -30819,17 +30669,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ đà kiềng trạm nước thải 2.1a-BP16.1a</t>
+          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ đà kiềng trạm xử lý nước thải (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -30871,17 +30721,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ BTCT nền trạm nước thải 2.1a-BP16.1a</t>
+          <t>Triển khai bản vẽ BTCT nền trạm xử lý nước thải (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -30923,17 +30773,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ nền trạm nước thải 2.1a-BP16.1a</t>
+          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ nền trạm xử lý nước thải (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -30975,17 +30825,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Trao đổi làm rõ thiếu xót thông tin thiết kế phần ngầm trạm nước thải 2.1a-BP16.1a, tập hợp soạn RFI nếu cần</t>
+          <t>Trao đổi làm rõ thiếu xót thông tin thiết kế phần ngầm trạm xử lý nước thải (Dự Án Mẫu), tập hợp soạn RFI nếu cần</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -31027,17 +30877,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Thực hiện điều chỉnh bản vẽ vách bể BP15.2 lần 1</t>
+          <t>Thực hiện điều chỉnh bản vẽ vách bể kỹ thuật (Dự Án Mẫu) lần 1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -31079,17 +30929,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Triển khai bảng khối lượng cốt thép vách bể BP15.2</t>
+          <t>Triển khai bảng khối lượng cốt thép vách bể kỹ thuật (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -31131,17 +30981,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Trao đổi làm rõ thiếu xót thông tin thiết kế phần vách bể  2.1a-BP16.1a, tập hợp soạn RFI nếu cần</t>
+          <t>Trao đổi làm rõ thiếu xót thông tin thiết kế phần vách bể trạm xử lý nước thải (Dự Án Mẫu), tập hợp soạn RFI nếu cần</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -31183,17 +31033,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D phần ngầm phục vụ phối hợp va chạm nhà xỉ than BP12  (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
+          <t>Triển khai mô hình 3D phần ngầm phục vụ phối hợp va chạm nhà phụ trợ kỹ thuật (Dự Án Mẫu) (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -31235,17 +31085,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ đà kiềng nhà xỉ than BP12</t>
+          <t>Triển khai bản vẽ đà kiềng nhà phụ trợ kỹ thuật (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -31287,17 +31137,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ đà kiềng nhà xỉ than BP12</t>
+          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ đà kiềng nhà phụ trợ kỹ thuật (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -31339,17 +31189,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Trao đổi làm rõ thiếu xót thông tin thiết kế phần ngầm nhà xỉ than BP12, tập hợp soạn RFI nếu cần</t>
+          <t>Trao đổi làm rõ thiếu xót thông tin thiết kế phần ngầm nhà phụ trợ kỹ thuật (Dự Án Mẫu), tập hợp soạn RFI nếu cần</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -31391,17 +31241,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D phần ngầm phục vụ phối hợp va chạm trạm nước thải BP15.1  (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
+          <t>Triển khai mô hình 3D phần ngầm phục vụ phối hợp va chạm trạm xử lý nước thải (Dự Án Mẫu) (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -31443,17 +31293,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ đà kiềng trạm nước thải BP15.1</t>
+          <t>Triển khai bản vẽ đà kiềng trạm xử lý nước thải (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -31495,17 +31345,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ đà kiềng trạm nước thải BP15.1</t>
+          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ đà kiềng trạm xử lý nước thải (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -31547,17 +31397,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D phần ngầm phục vụ phối hợp va chạm nhà nồi hơi BP12</t>
+          <t>Triển khai mô hình 3D phần ngầm phục vụ phối hợp va chạm nhà nồi hơi kỹ thuật (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -31599,17 +31449,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ đà kiềng nhà nồi hơi BP12</t>
+          <t>Triển khai bản vẽ đà kiềng nhà nồi hơi kỹ thuật (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -31651,17 +31501,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ đà kiềng nhà nồi hơi BP12</t>
+          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ đà kiềng nhà nồi hơi kỹ thuật (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -31703,17 +31553,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Trao đổi làm rõ thiếu xót thông tin thiết kế phần ngầm nhà nồi hơi BP12, tập hợp soạn RFI nếu cần</t>
+          <t>Trao đổi làm rõ thiếu xót thông tin thiết kế phần ngầm nhà nồi hơi kỹ thuật (Dự Án Mẫu), tập hợp soạn RFI nếu cần</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -31755,17 +31605,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Thực hiện điều chỉnh mô hình và bản vẽ Shop thoát nước mưa mái hạng mục  BP3 lần 1</t>
+          <t>Thực hiện điều chỉnh mô hình và bản vẽ Shop thoát nước mưa mái hạng mục mái xưởng A (Dự Án Mẫu) lần 1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -31807,17 +31657,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Thực hiện điều chỉnh mô hình và bản vẽ Shop thoát nước mưa mái hạng mục  MS1 lần 1</t>
+          <t>Thực hiện điều chỉnh mô hình và bản vẽ Shop thoát nước mưa mái hạng mục xưởng sản xuất (Dự Án Mẫu) lần 1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -31859,17 +31709,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Kiểm soát thiết kế kết cấu thép hạng mục MS1 cùng nhà thầu Fuji</t>
+          <t>Kiểm soát thiết kế kết cấu thép hạng mục xưởng sản xuất (Dự Án Mẫu) cùng Đơn vị gia công kết cấu thép</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -31907,17 +31757,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Kiểm soát thiết kế kết cấu thép hạng mục BP3, BP12 cùng nhà thầu CPT</t>
+          <t>Kiểm soát thiết kế kết cấu thép các hạng mục kết cấu thép Dự Án Mẫu cùng Đơn vị gia công kết cấu thép</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -31951,17 +31801,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D phần mái phục vụ phối hợp va chạm NP42</t>
+          <t>Triển khai mô hình 3D phần mái phục vụ phối hợp va chạm khu nhà điều hành (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -32003,17 +31853,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ BTCT sàn mái NP42</t>
+          <t>Triển khai bản vẽ BTCT sàn mái khu nhà điều hành (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -32055,17 +31905,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ BTCT sàn mái NP42</t>
+          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ BTCT sàn mái khu nhà điều hành (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -32107,12 +31957,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -32159,17 +32009,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ BTCT dầm mái NP42</t>
+          <t>Triển khai bản vẽ BTCT dầm mái khu nhà điều hành (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -32211,17 +32061,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ dầm BTCT tầng mái NP42</t>
+          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ dầm BTCT tầng mái khu nhà điều hành (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -32263,17 +32113,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Thực hiện điều chỉnh bộ bản vẽ dầm tầng mái TH2 lần 1</t>
+          <t>Thực hiện điều chỉnh bộ bản vẽ dầm tầng mái khu nhà xưởng B (Dự Án Mẫu) lần 1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -32315,17 +32165,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Thực hiện điều chỉnh bộ bản vẽ thang bộ  tầng mái TH1 lần 2</t>
+          <t>Thực hiện điều chỉnh bộ bản vẽ thang bộ tầng mái khu nhà xưởng A (Dự Án Mẫu) lần 2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -32367,17 +32217,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Thực hiện mô hình 3D tường xây TH2 (bao gồm lanh tô, bổ trụ, giằng tường, cửa) để phối hợp va chạm</t>
+          <t>Thực hiện mô hình 3D tường xây khu nhà xưởng B (Dự Án Mẫu) (bao gồm lanh tô, bổ trụ, giằng tường, cửa) để phối hợp va chạm</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -32419,17 +32269,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ Shop xây tô  tầng 1 TH2</t>
+          <t>Triển khai bản vẽ Shop xây tô tầng 1 khu nhà xưởng B (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -32471,12 +32321,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -32523,12 +32373,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -32575,12 +32425,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -32627,12 +32477,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -32679,12 +32529,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -32731,12 +32581,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -32783,12 +32633,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -32831,17 +32681,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Phối hợp soạn và cấp thông tin khối lương, mô hình, bản vẽ phục vụ IPC</t>
+          <t>Phối hợp soạn và cấp thông tin khối lương, mô hình, bản vẽ phục vụ hồ sơ nghiệm thu IPC (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -32875,12 +32725,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -32927,17 +32777,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ Shop hoàn thiện ốp lát nhà văn phòng các xưởng</t>
+          <t>Triển khai bản vẽ Shop hoàn thiện ốp lát khu văn phòng (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -32975,17 +32825,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng gạch ốp lát văn phòng các xưởng</t>
+          <t>Triển khai các bảng khối lượng gạch ốp lát khu văn phòng (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -33027,17 +32877,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D ốp lát hoàn thiện nhà vệ sinh 1,2</t>
+          <t>Triển khai mô hình 3D ốp lát hoàn thiện khu vệ sinh (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -33079,17 +32929,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ Shop hoàn thiện ốp lát nhà vệ sinh 1,2</t>
+          <t>Triển khai bản vẽ Shop hoàn thiện ốp lát khu vệ sinh (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -33127,17 +32977,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng gạch ốp lát nhà vệ sinh 1,2</t>
+          <t>Triển khai các bảng khối lượng gạch ốp lát khu vệ sinh (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -33179,17 +33029,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D ốp lát hoàn thiện nhà  bảo vệ 1,2</t>
+          <t>Triển khai mô hình 3D ốp lát hoàn thiện nhà bảo vệ (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -33231,17 +33081,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ Shop hoàn thiện ốp lát nhà bảo vệ 1,2</t>
+          <t>Triển khai bản vẽ Shop hoàn thiện ốp lát nhà bảo vệ (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -33279,17 +33129,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng gạch ốp lát nhà bảo vệ 1,2</t>
+          <t>Triển khai các bảng khối lượng gạch ốp lát nhà bảo vệ (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -33331,12 +33181,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -33379,12 +33229,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -33431,17 +33281,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Điều chỉnh và phát hành mô hình 3D cho tất cả các thay đổi thiết kế dự án</t>
+          <t>Điều chỉnh và phát hành mô hình 3D cho tất cả các thay đổi thiết kế Dự Án Mẫu</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -33483,17 +33333,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D phần  phục vụ phối hợp va chạm nhà phụ trợ 1 (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
+          <t>Triển khai mô hình 3D phần phục vụ phối hợp va chạm nhà phụ trợ kỹ thuật (Dự Án Mẫu) (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -33535,17 +33385,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ Shop đà kiềng và nền bể chứa và bể XLNT nhà phụ trợ 1</t>
+          <t>Triển khai bản vẽ Shop đà kiềng và nền bể chứa và bể XLNT nhà phụ trợ kỹ thuật (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -33587,17 +33437,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ đà kiềng và nền nhà phụ trợ 1</t>
+          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ đà kiềng và nền nhà phụ trợ kỹ thuật (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -33631,12 +33481,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -33683,12 +33533,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -33735,12 +33585,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -33787,12 +33637,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -33835,12 +33685,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -33879,12 +33729,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -33923,12 +33773,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -33967,12 +33817,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -34011,12 +33861,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -34055,17 +33905,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Triển  khai các bảng khối lương hệ thống điện hạ tầng</t>
+          <t>Triển khai các bảng khối lương hệ thống điện hạ tầng</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -34099,17 +33949,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Kiểm soát thiết kế kết cấu thép nhà xưởng E, G, H</t>
+          <t>Kiểm soát thiết kế kết cấu thép cụm nhà xưởng mở rộng (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -34143,17 +33993,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Kiểm soát thiết kế kết cấu thép các xưởng A, B, C, D, F cùng nhà thầu Đại Dũng</t>
+          <t>Kiểm soát thiết kế kết cấu thép cụm nhà xưởng sản xuất chính (Dự Án Mẫu) cùng Đơn vị gia công kết cấu thép</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -34187,17 +34037,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Triẻn khai mô hình 3D phục vụ phối hợp va chạm phần ngầm bể tự hoại  (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý) (tách 2 gói)</t>
+          <t>Triẻn khai mô hình 3D phục vụ phối hợp va chạm phần ngầm bể tự hoại (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý) (tách 2 gói)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -34239,12 +34089,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -34291,12 +34141,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -34343,12 +34193,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -34395,17 +34245,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Thực hiện điều chỉnh bản vẽ Shop móng và cổ cột 2 gói 3.2B và 3.2C theo yêu cầu BCH (tách gói, chạy tọa độ)</t>
+          <t>Thực hiện điều chỉnh bản vẽ Shop móng và cổ cột các phân đoạn móng (Dự Án Mẫu) theo yêu cầu BCH (tách gói, chạy tọa độ)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -34447,17 +34297,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng bê tông, cốt thép móng và cổ cột cho 3.2B và 3.2C</t>
+          <t>Triển khai các bảng khối lượng bê tông, cốt thép móng và cổ cột cho các phân đoạn móng (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -34499,12 +34349,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -34551,17 +34401,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Thực hiện điều chỉnh bản vẽ Shop móng và cổ cột 2 gói 3.2B và 3.2C theo comments TVGS lần 1</t>
+          <t>Thực hiện điều chỉnh bản vẽ Shop móng và cổ cột các phân đoạn móng (Dự Án Mẫu) theo comments TVGS lần 1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -34599,12 +34449,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -34647,17 +34497,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D xây tô hà trạm 1,2,3,4 (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
+          <t>Triển khai mô hình 3D xây tô nhà trạm kỹ thuật (Dự Án Mẫu) (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -34699,17 +34549,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ shop xây tô nhà trạm 1,2,3,4</t>
+          <t>Triển khai bản vẽ shop xây tô nhà trạm kỹ thuật (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -34751,17 +34601,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng xây tô nhà trạm 1,2,3,4</t>
+          <t>Triển khai các bảng khối lượng xây tô nhà trạm kỹ thuật (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -34803,17 +34653,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D ốp lát nhà vệ sinh trạm nguồn 1,2,3,4 (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
+          <t>Triển khai mô hình 3D ốp lát nhà vệ sinh trạm nguồn điện kỹ thuật (Dự Án Mẫu) (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -34855,17 +34705,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ shop ốp lát nhà vệ sinh trạm nguồn 1,2,3,4</t>
+          <t>Triển khai bản vẽ shop ốp lát nhà vệ sinh trạm nguồn điện kỹ thuật (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -34907,17 +34757,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng ốp lát nhà trạm nguồn 1,2,3,4</t>
+          <t>Triển khai các bảng khối lượng ốp lát trạm nguồn điện kỹ thuật (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -34959,17 +34809,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Triển khai bảng khối lượng chi tiết trạm nguồn phục vụ triển khai IPC1</t>
+          <t>Triển khai bảng khối lượng chi tiết trạm nguồn điện kỹ thuật (Dự Án Mẫu) phục vụ hồ sơ nghiệm thu IPC (Dự Án Mẫu)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -35011,12 +34861,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -35063,12 +34913,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Dự án Mẫu (Thi công &amp; Triển khai)</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dự án Mẫu</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -36165,7 +36015,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Chuẩn hoá thiết kế kiến trúc  các hạng mục</t>
+          <t>Chuẩn hoá thiết kế kiến trúc các hạng mục</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -38981,7 +38831,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Biểu mẫu câu hỏi làm rõ thông tin kĩ thuật  đầu vào khi triển khai dự án</t>
+          <t>Biểu mẫu câu hỏi làm rõ thông tin kĩ thuật đầu vào khi triển khai dự án</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -39773,7 +39623,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Biểu mẫu câu hỏi làm rõ thông tin kĩ thuật  đầu vào khi triển khai dự án</t>
+          <t>Biểu mẫu câu hỏi làm rõ thông tin kĩ thuật đầu vào khi triển khai dự án</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">

--- a/BIM_TK_PowerBI_DataModel_2026.xlsx
+++ b/BIM_TK_PowerBI_DataModel_2026.xlsx
@@ -30570,12 +30570,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D phần ngầm phục vụ phối hợp va chạm trạm xử lý nước thải (Dự Án Mẫu) (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
+          <t>Triển khai mô hình 3D phần ngầm phục vụ phối hợp va chạm trạm xử lý nước thải (Dự Án Mẫu 02) (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -30622,12 +30622,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ đà kiềng trạm xử lý nước thải (Dự Án Mẫu)</t>
+          <t>Triển khai bản vẽ đà kiềng trạm xử lý nước thải (Dự Án Mẫu 02)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -30674,12 +30674,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ đà kiềng trạm xử lý nước thải (Dự Án Mẫu)</t>
+          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ đà kiềng trạm xử lý nước thải (Dự Án Mẫu 02)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -30726,12 +30726,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ BTCT nền trạm xử lý nước thải (Dự Án Mẫu)</t>
+          <t>Triển khai bản vẽ BTCT nền trạm xử lý nước thải (Dự Án Mẫu 02)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -30778,12 +30778,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ nền trạm xử lý nước thải (Dự Án Mẫu)</t>
+          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ nền trạm xử lý nước thải (Dự Án Mẫu 02)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -30830,12 +30830,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Trao đổi làm rõ thiếu xót thông tin thiết kế phần ngầm trạm xử lý nước thải (Dự Án Mẫu), tập hợp soạn RFI nếu cần</t>
+          <t>Trao đổi làm rõ thiếu xót thông tin thiết kế phần ngầm trạm xử lý nước thải (Dự Án Mẫu 02), tập hợp soạn RFI nếu cần</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -30882,12 +30882,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Thực hiện điều chỉnh bản vẽ vách bể kỹ thuật (Dự Án Mẫu) lần 1</t>
+          <t>Thực hiện điều chỉnh bản vẽ vách bể kỹ thuật (Dự Án Mẫu 02) lần 1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -30934,12 +30934,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Triển khai bảng khối lượng cốt thép vách bể kỹ thuật (Dự Án Mẫu)</t>
+          <t>Triển khai bảng khối lượng cốt thép vách bể kỹ thuật (Dự Án Mẫu 02)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -30986,12 +30986,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Trao đổi làm rõ thiếu xót thông tin thiết kế phần vách bể trạm xử lý nước thải (Dự Án Mẫu), tập hợp soạn RFI nếu cần</t>
+          <t>Trao đổi làm rõ thiếu xót thông tin thiết kế phần vách bể trạm xử lý nước thải (Dự Án Mẫu 02), tập hợp soạn RFI nếu cần</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -31038,12 +31038,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D phần ngầm phục vụ phối hợp va chạm nhà phụ trợ kỹ thuật (Dự Án Mẫu) (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
+          <t>Triển khai mô hình 3D phần ngầm phục vụ phối hợp va chạm nhà phụ trợ kỹ thuật (Dự Án Mẫu 02) (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -31090,12 +31090,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ đà kiềng nhà phụ trợ kỹ thuật (Dự Án Mẫu)</t>
+          <t>Triển khai bản vẽ đà kiềng nhà phụ trợ kỹ thuật (Dự Án Mẫu 02)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -31142,12 +31142,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 01</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ đà kiềng nhà phụ trợ kỹ thuật (Dự Án Mẫu)</t>
+          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ đà kiềng nhà phụ trợ kỹ thuật (Dự Án Mẫu 02)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -31194,12 +31194,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 01</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Trao đổi làm rõ thiếu xót thông tin thiết kế phần ngầm nhà phụ trợ kỹ thuật (Dự Án Mẫu), tập hợp soạn RFI nếu cần</t>
+          <t>Trao đổi làm rõ thiếu xót thông tin thiết kế phần ngầm nhà phụ trợ kỹ thuật (Dự Án Mẫu 02), tập hợp soạn RFI nếu cần</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -31246,12 +31246,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D phần ngầm phục vụ phối hợp va chạm trạm xử lý nước thải (Dự Án Mẫu) (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
+          <t>Triển khai mô hình 3D phần ngầm phục vụ phối hợp va chạm trạm xử lý nước thải (Dự Án Mẫu 02) (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 01</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ đà kiềng trạm xử lý nước thải (Dự Án Mẫu)</t>
+          <t>Triển khai bản vẽ đà kiềng trạm xử lý nước thải (Dự Án Mẫu 02)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -31350,12 +31350,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 01</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ đà kiềng trạm xử lý nước thải (Dự Án Mẫu)</t>
+          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ đà kiềng trạm xử lý nước thải (Dự Án Mẫu 02)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -31402,12 +31402,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 01</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D phần ngầm phục vụ phối hợp va chạm nhà nồi hơi kỹ thuật (Dự Án Mẫu)</t>
+          <t>Triển khai mô hình 3D phần ngầm phục vụ phối hợp va chạm nhà nồi hơi kỹ thuật (Dự Án Mẫu 02)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -31454,12 +31454,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 01</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ đà kiềng nhà nồi hơi kỹ thuật (Dự Án Mẫu)</t>
+          <t>Triển khai bản vẽ đà kiềng nhà nồi hơi kỹ thuật (Dự Án Mẫu 02)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -31506,12 +31506,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 01</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ đà kiềng nhà nồi hơi kỹ thuật (Dự Án Mẫu)</t>
+          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ đà kiềng nhà nồi hơi kỹ thuật (Dự Án Mẫu 02)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -31558,12 +31558,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 01</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Trao đổi làm rõ thiếu xót thông tin thiết kế phần ngầm nhà nồi hơi kỹ thuật (Dự Án Mẫu), tập hợp soạn RFI nếu cần</t>
+          <t>Trao đổi làm rõ thiếu xót thông tin thiết kế phần ngầm nhà nồi hơi kỹ thuật (Dự Án Mẫu 02), tập hợp soạn RFI nếu cần</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -31610,12 +31610,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 01</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Thực hiện điều chỉnh mô hình và bản vẽ Shop thoát nước mưa mái hạng mục mái xưởng A (Dự Án Mẫu) lần 1</t>
+          <t>Thực hiện điều chỉnh mô hình và bản vẽ Shop thoát nước mưa mái hạng mục mái xưởng A (Dự Án Mẫu 03) lần 1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -31662,12 +31662,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 01</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Thực hiện điều chỉnh mô hình và bản vẽ Shop thoát nước mưa mái hạng mục xưởng sản xuất (Dự Án Mẫu) lần 1</t>
+          <t>Thực hiện điều chỉnh mô hình và bản vẽ Shop thoát nước mưa mái hạng mục xưởng sản xuất (Dự Án Mẫu 03) lần 1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -31714,12 +31714,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 01</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Kiểm soát thiết kế kết cấu thép hạng mục xưởng sản xuất (Dự Án Mẫu) cùng Đơn vị gia công kết cấu thép</t>
+          <t>Kiểm soát thiết kế kết cấu thép hạng mục xưởng sản xuất (Dự Án Mẫu 03) cùng Đơn vị gia công kết cấu thép</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -31762,12 +31762,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Kiểm soát thiết kế kết cấu thép các hạng mục kết cấu thép Dự Án Mẫu cùng Đơn vị gia công kết cấu thép</t>
+          <t>Kiểm soát thiết kế kết cấu thép các hạng mục kết cấu thép (Dự Án Mẫu 03) cùng Đơn vị gia công kết cấu thép</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -31806,12 +31806,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 04</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D phần mái phục vụ phối hợp va chạm khu nhà điều hành (Dự Án Mẫu)</t>
+          <t>Triển khai mô hình 3D phần mái phục vụ phối hợp va chạm khu nhà điều hành (Dự Án Mẫu 03)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -31858,12 +31858,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 04</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ BTCT sàn mái khu nhà điều hành (Dự Án Mẫu)</t>
+          <t>Triển khai bản vẽ BTCT sàn mái khu nhà điều hành (Dự Án Mẫu 03)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -31910,12 +31910,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 04</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ BTCT sàn mái khu nhà điều hành (Dự Án Mẫu)</t>
+          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ BTCT sàn mái khu nhà điều hành (Dự Án Mẫu 03)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -31962,7 +31962,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 04</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -32014,12 +32014,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 04</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ BTCT dầm mái khu nhà điều hành (Dự Án Mẫu)</t>
+          <t>Triển khai bản vẽ BTCT dầm mái khu nhà điều hành (Dự Án Mẫu 03)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -32066,12 +32066,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 04</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ dầm BTCT tầng mái khu nhà điều hành (Dự Án Mẫu)</t>
+          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ dầm BTCT tầng mái khu nhà điều hành (Dự Án Mẫu 03)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -32118,12 +32118,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 04</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Thực hiện điều chỉnh bộ bản vẽ dầm tầng mái khu nhà xưởng B (Dự Án Mẫu) lần 1</t>
+          <t>Thực hiện điều chỉnh bộ bản vẽ dầm tầng mái khu nhà xưởng B (Dự Án Mẫu 04) lần 1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -32170,12 +32170,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 04</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Thực hiện điều chỉnh bộ bản vẽ thang bộ tầng mái khu nhà xưởng A (Dự Án Mẫu) lần 2</t>
+          <t>Thực hiện điều chỉnh bộ bản vẽ thang bộ tầng mái khu nhà xưởng A (Dự Án Mẫu 04) lần 2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -32222,12 +32222,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 04</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Thực hiện mô hình 3D tường xây khu nhà xưởng B (Dự Án Mẫu) (bao gồm lanh tô, bổ trụ, giằng tường, cửa) để phối hợp va chạm</t>
+          <t>Thực hiện mô hình 3D tường xây khu nhà xưởng B (Dự Án Mẫu 04) (bao gồm lanh tô, bổ trụ, giằng tường, cửa) để phối hợp va chạm</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -32274,12 +32274,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 04</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ Shop xây tô tầng 1 khu nhà xưởng B (Dự Án Mẫu)</t>
+          <t>Triển khai bản vẽ Shop xây tô tầng 1 khu nhà xưởng B (Dự Án Mẫu 04)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -32326,7 +32326,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 04</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -32378,7 +32378,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 04</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -32430,7 +32430,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 02</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -32482,7 +32482,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 02</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -32534,7 +32534,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 02</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -32586,7 +32586,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 02</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -32638,7 +32638,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 02</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -32686,12 +32686,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 02</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Phối hợp soạn và cấp thông tin khối lương, mô hình, bản vẽ phục vụ hồ sơ nghiệm thu IPC (Dự Án Mẫu)</t>
+          <t>Phối hợp soạn và cấp thông tin khối lương, mô hình, bản vẽ phục vụ hồ sơ nghiệm thu IPC (Dự Án Mẫu 05)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -32730,7 +32730,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 02</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -32782,12 +32782,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 02</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ Shop hoàn thiện ốp lát khu văn phòng (Dự Án Mẫu)</t>
+          <t>Triển khai bản vẽ Shop hoàn thiện ốp lát khu văn phòng xưởng (Dự Án Mẫu 01)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -32830,12 +32830,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 02</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng gạch ốp lát khu văn phòng (Dự Án Mẫu)</t>
+          <t>Triển khai các bảng khối lượng gạch ốp lát khu văn phòng xưởng (Dự Án Mẫu 01)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -32882,12 +32882,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 02</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D ốp lát hoàn thiện khu vệ sinh (Dự Án Mẫu)</t>
+          <t>Triển khai mô hình 3D ốp lát hoàn thiện khu vệ sinh (Dự Án Mẫu 01)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -32934,12 +32934,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 02</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ Shop hoàn thiện ốp lát khu vệ sinh (Dự Án Mẫu)</t>
+          <t>Triển khai bản vẽ Shop hoàn thiện ốp lát khu vệ sinh (Dự Án Mẫu 01)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -32982,12 +32982,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 02</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng gạch ốp lát khu vệ sinh (Dự Án Mẫu)</t>
+          <t>Triển khai các bảng khối lượng gạch ốp lát khu vệ sinh (Dự Án Mẫu 01)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -33034,12 +33034,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 02</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D ốp lát hoàn thiện nhà bảo vệ (Dự Án Mẫu)</t>
+          <t>Triển khai mô hình 3D ốp lát hoàn thiện nhà bảo vệ (Dự Án Mẫu 01)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -33086,12 +33086,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 02</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ Shop hoàn thiện ốp lát nhà bảo vệ (Dự Án Mẫu)</t>
+          <t>Triển khai bản vẽ Shop hoàn thiện ốp lát nhà bảo vệ (Dự Án Mẫu 01)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -33134,12 +33134,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 02</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng gạch ốp lát nhà bảo vệ (Dự Án Mẫu)</t>
+          <t>Triển khai các bảng khối lượng gạch ốp lát nhà bảo vệ (Dự Án Mẫu 01)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -33186,7 +33186,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 02</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -33234,7 +33234,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 02</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -33286,12 +33286,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 02</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Điều chỉnh và phát hành mô hình 3D cho tất cả các thay đổi thiết kế Dự Án Mẫu</t>
+          <t>Điều chỉnh và phát hành mô hình 3D cho tất cả các thay đổi thiết kế dự án mẫu</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -33338,12 +33338,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 03</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D phần phục vụ phối hợp va chạm nhà phụ trợ kỹ thuật (Dự Án Mẫu) (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
+          <t>Triển khai mô hình 3D phần phục vụ phối hợp va chạm nhà phụ trợ kỹ thuật (Dự Án Mẫu 01) (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -33390,12 +33390,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 03</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ Shop đà kiềng và nền bể chứa và bể XLNT nhà phụ trợ kỹ thuật (Dự Án Mẫu)</t>
+          <t>Triển khai bản vẽ Shop đà kiềng và nền bể chứa và bể XLNT nhà phụ trợ kỹ thuật (Dự Án Mẫu 01)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -33442,12 +33442,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 03</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ đà kiềng và nền nhà phụ trợ kỹ thuật (Dự Án Mẫu)</t>
+          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ đà kiềng và nền nhà phụ trợ kỹ thuật (Dự Án Mẫu 01)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -33486,7 +33486,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 03</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -33538,7 +33538,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 03</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -33590,7 +33590,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 03</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -33642,7 +33642,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 03</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -33690,7 +33690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 03</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -33734,7 +33734,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 03</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -33778,7 +33778,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 03</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -33822,7 +33822,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 03</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -33866,7 +33866,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 03</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -33910,7 +33910,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 03</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -33954,12 +33954,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 03</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Kiểm soát thiết kế kết cấu thép cụm nhà xưởng mở rộng (Dự Án Mẫu)</t>
+          <t>Kiểm soát thiết kế kết cấu thép cụm nhà xưởng mở rộng (Dự Án Mẫu 01)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -33998,12 +33998,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 03</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Kiểm soát thiết kế kết cấu thép cụm nhà xưởng sản xuất chính (Dự Án Mẫu) cùng Đơn vị gia công kết cấu thép</t>
+          <t>Kiểm soát thiết kế kết cấu thép cụm nhà xưởng sản xuất chính (Dự Án Mẫu 01) cùng Đơn vị gia công kết cấu thép</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -34042,7 +34042,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 05</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -34094,7 +34094,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 05</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -34146,7 +34146,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 05</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -34198,7 +34198,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 05</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -34250,12 +34250,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 05</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Thực hiện điều chỉnh bản vẽ Shop móng và cổ cột các phân đoạn móng (Dự Án Mẫu) theo yêu cầu BCH (tách gói, chạy tọa độ)</t>
+          <t>Thực hiện điều chỉnh bản vẽ Shop móng và cổ cột các phân đoạn móng (Dự Án Mẫu 07) theo yêu cầu BCH (tách gói, chạy tọa độ)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -34302,12 +34302,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 05</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng bê tông, cốt thép móng và cổ cột cho các phân đoạn móng (Dự Án Mẫu)</t>
+          <t>Triển khai các bảng khối lượng bê tông, cốt thép móng và cổ cột cho các phân đoạn móng (Dự Án Mẫu 07)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -34354,7 +34354,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 05</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -34406,12 +34406,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 05</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Thực hiện điều chỉnh bản vẽ Shop móng và cổ cột các phân đoạn móng (Dự Án Mẫu) theo comments TVGS lần 1</t>
+          <t>Thực hiện điều chỉnh bản vẽ Shop móng và cổ cột các phân đoạn móng (Dự Án Mẫu 07) theo comments TVGS lần 1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 05</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -34502,12 +34502,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 06</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D xây tô nhà trạm kỹ thuật (Dự Án Mẫu) (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
+          <t>Triển khai mô hình 3D xây tô nhà trạm kỹ thuật (Dự Án Mẫu 06) (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -34554,12 +34554,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 06</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ shop xây tô nhà trạm kỹ thuật (Dự Án Mẫu)</t>
+          <t>Triển khai bản vẽ shop xây tô nhà trạm kỹ thuật (Dự Án Mẫu 06)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -34606,12 +34606,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 06</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng xây tô nhà trạm kỹ thuật (Dự Án Mẫu)</t>
+          <t>Triển khai các bảng khối lượng xây tô nhà trạm kỹ thuật (Dự Án Mẫu 06)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -34658,12 +34658,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 06</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D ốp lát nhà vệ sinh trạm nguồn điện kỹ thuật (Dự Án Mẫu) (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
+          <t>Triển khai mô hình 3D ốp lát nhà vệ sinh trạm nguồn điện kỹ thuật (Dự Án Mẫu 06) (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -34710,12 +34710,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 06</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ shop ốp lát nhà vệ sinh trạm nguồn điện kỹ thuật (Dự Án Mẫu)</t>
+          <t>Triển khai bản vẽ shop ốp lát nhà vệ sinh trạm nguồn điện kỹ thuật (Dự Án Mẫu 06)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -34762,12 +34762,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 06</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng ốp lát trạm nguồn điện kỹ thuật (Dự Án Mẫu)</t>
+          <t>Triển khai các bảng khối lượng ốp lát trạm nguồn điện kỹ thuật (Dự Án Mẫu 06)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -34814,12 +34814,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 06</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Triển khai bảng khối lượng chi tiết trạm nguồn điện kỹ thuật (Dự Án Mẫu) phục vụ hồ sơ nghiệm thu IPC (Dự Án Mẫu)</t>
+          <t>Triển khai bảng khối lượng chi tiết trạm nguồn điện kỹ thuật (Dự Án Mẫu 06) phục vụ hồ sơ nghiệm thu IPC (Dự Án Mẫu 05)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -34866,7 +34866,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 07</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -34918,7 +34918,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu</t>
+          <t>Dự Án Mẫu 07</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">

--- a/BIM_TK_PowerBI_DataModel_2026.xlsx
+++ b/BIM_TK_PowerBI_DataModel_2026.xlsx
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Nhân sự D (Lead Kết Cấu)</t>
+          <t>Lead Bộ môn Kết cấu</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>KS Triển khai KC &amp; 3 KS BIM KC (Nhân sự J, K...)</t>
+          <t>2 KS Thiết kế &amp; 3 KS BIM Kết cấu</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nhân sự E</t>
+          <t>Lead Bộ môn Kiến trúc</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KTS Triển khai &amp; 3 KS BIM KT (Nhân sự H, I...)</t>
+          <t>1 KTS Thiết kế &amp; 3 KS BIM Kiến trúc</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Nhân sự C (Lead BIM MEPF)</t>
+          <t>Lead Bộ môn BIM MEPF</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KS Cơ Điện &amp; 3 KS BIM MEP (Nhân sự L &amp; KS MEP)</t>
+          <t>1 KS TK + 1 KS MEP + 3 KS BIM MEP</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Nhân sự G</t>
+          <t>Lead Bộ môn HVAC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>KS Triển khai HVAC</t>
+          <t>1 KS Triển khai HVAC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Lead Kỹ thuật Hạ tầng &amp; CDE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2 KS BIM Hạ tầng &amp; CDE (Điều phối chia đều sang)</t>
+          <t>2 KS BIM Hạ tầng &amp; CDE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4933,12 +4933,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6285,7 +6285,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6337,12 +6337,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -8677,12 +8677,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8729,7 +8729,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -9145,12 +9145,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -9249,7 +9249,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -9613,12 +9613,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -10081,12 +10081,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -10185,7 +10185,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -10237,7 +10237,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -10445,7 +10445,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -10497,7 +10497,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -10705,7 +10705,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -10913,7 +10913,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -11017,12 +11017,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11069,7 +11069,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -11225,7 +11225,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -11485,12 +11485,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11537,7 +11537,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -11589,7 +11589,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -11641,7 +11641,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -11745,7 +11745,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -11797,7 +11797,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -11901,7 +11901,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -11953,12 +11953,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -12161,7 +12161,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -12369,7 +12369,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12473,7 +12473,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -12629,7 +12629,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -12733,7 +12733,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -12837,7 +12837,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -12889,12 +12889,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -13045,7 +13045,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -13097,7 +13097,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -13201,7 +13201,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -13253,7 +13253,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13409,7 +13409,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -13617,7 +13617,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -13669,7 +13669,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -13773,7 +13773,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -13825,12 +13825,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -13877,7 +13877,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -13981,7 +13981,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -14033,7 +14033,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -14085,7 +14085,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -14137,7 +14137,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -14293,12 +14293,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -14345,7 +14345,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -14397,7 +14397,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -14449,7 +14449,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -14501,7 +14501,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -14605,7 +14605,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -14657,7 +14657,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -14709,7 +14709,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -14813,7 +14813,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -14865,7 +14865,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -14917,7 +14917,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -14969,7 +14969,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -15021,7 +15021,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -15073,7 +15073,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -15125,7 +15125,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -15177,7 +15177,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -15385,7 +15385,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -15541,7 +15541,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -15593,7 +15593,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -15645,7 +15645,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -15697,12 +15697,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -15801,7 +15801,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -15853,7 +15853,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -15905,7 +15905,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -15957,7 +15957,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -16009,7 +16009,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -16061,7 +16061,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -16165,12 +16165,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -16217,7 +16217,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -16321,7 +16321,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -16425,7 +16425,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -16477,7 +16477,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -16529,7 +16529,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -16581,7 +16581,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -16633,12 +16633,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -16685,7 +16685,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -16737,7 +16737,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -16789,7 +16789,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -16893,7 +16893,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -16945,7 +16945,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -16997,7 +16997,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -17049,7 +17049,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -17101,12 +17101,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -17153,7 +17153,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -17205,7 +17205,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -17257,7 +17257,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -17309,7 +17309,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -17361,7 +17361,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -17465,7 +17465,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -17569,12 +17569,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Nhân sự A</t>
+          <t>Trưởng bộ phận BIM - TK</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>TBP BIM-TK</t>
+          <t>Ban Quản lý</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -17621,7 +17621,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Nhân sự B</t>
+          <t>Lead BIM Kiến Trúc</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -17673,7 +17673,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Nhân sự H</t>
+          <t>Kỹ sư BIM Kiến Trúc 1</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -17725,7 +17725,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Nhân sự I</t>
+          <t>Kỹ sư BIM Kiến Trúc 2</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -17777,7 +17777,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Nhân sự J</t>
+          <t>Kỹ sư BIM Kết Cấu 1</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -17829,7 +17829,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Nhân sự K</t>
+          <t>Kỹ sư BIM Kết Cấu 2</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -17881,7 +17881,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Nhân sự C</t>
+          <t>Lead BIM MEPF</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
@@ -17933,7 +17933,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Nhân sự L</t>
+          <t>Kỹ sư BIM MEPF</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -17985,7 +17985,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Nhân sự M</t>
+          <t>Kỹ sư BIM Hạ Tầng &amp; CDE</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -18988,7 +18988,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nhân sự D</t>
+          <t>Lead Kết Cấu</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -19051,7 +19051,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Nhân sự D</t>
+          <t>Lead Kết Cấu</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -19114,7 +19114,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Nhân sự D</t>
+          <t>Lead Kết Cấu</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -19177,7 +19177,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nhân sự D</t>
+          <t>Lead Kết Cấu</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -19240,7 +19240,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Nhân sự D</t>
+          <t>Lead Kết Cấu</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -19303,7 +19303,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Nhân sự D</t>
+          <t>Lead Kết Cấu</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -19366,7 +19366,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Nhân sự D</t>
+          <t>Lead Kết Cấu</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -19429,7 +19429,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Nhân sự D</t>
+          <t>Lead Kết Cấu</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -19492,7 +19492,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Nhân sự D</t>
+          <t>Lead Kết Cấu</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -19555,7 +19555,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Nhân sự D</t>
+          <t>Lead Kết Cấu</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -19618,7 +19618,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nhân sự D</t>
+          <t>Lead Kết Cấu</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -19681,7 +19681,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nhân sự D</t>
+          <t>Lead Kết Cấu</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -19744,7 +19744,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Nhân sự D</t>
+          <t>Lead Kết Cấu</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -19807,7 +19807,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Nhân sự D</t>
+          <t>Lead Kết Cấu</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -19870,7 +19870,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nhân sự D</t>
+          <t>Lead Kết Cấu</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -19933,7 +19933,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Nhân sự D</t>
+          <t>Lead Kết Cấu</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -19996,7 +19996,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Nhân sự D</t>
+          <t>Lead Kết Cấu</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Nhân sự D</t>
+          <t>Lead Kết Cấu</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -20122,7 +20122,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Nhân sự D</t>
+          <t>Lead Kết Cấu</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -20185,7 +20185,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Nhân sự D</t>
+          <t>Lead Kết Cấu</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -20248,7 +20248,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Nhân sự D</t>
+          <t>Lead Kết Cấu</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Nhân sự D</t>
+          <t>Lead Kết Cấu</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Nhân sự D</t>
+          <t>Lead Kết Cấu</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -20437,7 +20437,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Nhân sự E</t>
+          <t>Lead Kiến Trúc</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -20500,7 +20500,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Nhân sự E</t>
+          <t>Lead Kiến Trúc</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -20563,7 +20563,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Nhân sự E</t>
+          <t>Lead Kiến Trúc</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -20626,7 +20626,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Nhân sự E</t>
+          <t>Lead Kiến Trúc</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -20689,7 +20689,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Nhân sự E</t>
+          <t>Lead Kiến Trúc</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Nhân sự E</t>
+          <t>Lead Kiến Trúc</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -20815,7 +20815,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Nhân sự E</t>
+          <t>Lead Kiến Trúc</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -20878,7 +20878,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Nhân sự E</t>
+          <t>Lead Kiến Trúc</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -20941,7 +20941,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Nhân sự E</t>
+          <t>Lead Kiến Trúc</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -21004,7 +21004,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Nhân sự E</t>
+          <t>Lead Kiến Trúc</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -21067,7 +21067,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Nhân sự E</t>
+          <t>Lead Kiến Trúc</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -21130,7 +21130,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Nhân sự E</t>
+          <t>Lead Kiến Trúc</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -21193,7 +21193,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Nhân sự E</t>
+          <t>Lead Kiến Trúc</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -21256,7 +21256,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Nhân sự E</t>
+          <t>Lead Kiến Trúc</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -21319,7 +21319,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Nhân sự E</t>
+          <t>Lead Kiến Trúc</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -21382,7 +21382,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Nhân sự E</t>
+          <t>Lead Kiến Trúc</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -21445,7 +21445,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Nhân sự E</t>
+          <t>Lead Kiến Trúc</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -21508,7 +21508,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Nhân sự E</t>
+          <t>Lead Kiến Trúc</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -21571,7 +21571,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Nhân sự E</t>
+          <t>Lead Kiến Trúc</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -21634,7 +21634,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Nhân sự E</t>
+          <t>Lead Kiến Trúc</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -21697,7 +21697,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Điện</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -21760,7 +21760,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Điện</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -21823,7 +21823,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Điện</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -21886,7 +21886,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Điện</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -21949,7 +21949,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Điện</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -22012,7 +22012,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Điện</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -22075,7 +22075,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Điện</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -22138,7 +22138,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Điện</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -22201,7 +22201,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Điện</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -22264,7 +22264,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Điện</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -22327,7 +22327,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Điện</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -22390,7 +22390,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Điện</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -22453,7 +22453,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Điện</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -22516,7 +22516,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Điện</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -22579,7 +22579,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Điện</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -22642,7 +22642,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Điện</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -22705,7 +22705,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Điện</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -22768,7 +22768,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Điện</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -22831,7 +22831,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Nhân sự G</t>
+          <t>Lead HVAC</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -22894,7 +22894,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Nhân sự G</t>
+          <t>Lead HVAC</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -22957,7 +22957,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Nhân sự G</t>
+          <t>Lead HVAC</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -23020,7 +23020,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Nhân sự G</t>
+          <t>Lead HVAC</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -23083,7 +23083,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Nhân sự G</t>
+          <t>Lead HVAC</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -23146,7 +23146,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Nhân sự G</t>
+          <t>Lead HVAC</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -23209,7 +23209,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Nhân sự G</t>
+          <t>Lead HVAC</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -23272,7 +23272,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Nhân sự G</t>
+          <t>Lead HVAC</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -23335,7 +23335,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Nhân sự G</t>
+          <t>Lead HVAC</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -23398,7 +23398,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Nhân sự G</t>
+          <t>Lead HVAC</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -23461,7 +23461,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Nhân sự G</t>
+          <t>Lead HVAC</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -23524,7 +23524,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Nhân sự G</t>
+          <t>Lead HVAC</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -23587,7 +23587,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Nhân sự G</t>
+          <t>Lead HVAC</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -23650,7 +23650,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Nhân sự G</t>
+          <t>Lead HVAC</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -23713,7 +23713,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Nhân sự G</t>
+          <t>Lead HVAC</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -23776,7 +23776,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Nhân sự G</t>
+          <t>Lead HVAC</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -23839,7 +23839,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Nhân sự G</t>
+          <t>Lead HVAC</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -23902,7 +23902,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Nhân sự G</t>
+          <t>Lead HVAC</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -23965,7 +23965,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Cấp Thoát Nước</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -24028,7 +24028,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Cấp Thoát Nước</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -24091,7 +24091,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Cấp Thoát Nước</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -24154,7 +24154,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Cấp Thoát Nước</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -24217,7 +24217,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Cấp Thoát Nước</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -24280,7 +24280,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Cấp Thoát Nước</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -24343,7 +24343,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Cấp Thoát Nước</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -24406,7 +24406,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Cấp Thoát Nước</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -24469,7 +24469,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Cấp Thoát Nước</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -24532,7 +24532,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Cấp Thoát Nước</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -24595,7 +24595,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Cấp Thoát Nước</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -24658,7 +24658,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Cấp Thoát Nước</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -24721,7 +24721,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Cấp Thoát Nước</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -24784,7 +24784,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Cấp Thoát Nước</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -24847,7 +24847,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Cấp Thoát Nước</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -24910,7 +24910,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Cấp Thoát Nước</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -24973,7 +24973,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Cấp Thoát Nước</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -25036,7 +25036,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead Cấp Thoát Nước</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -25099,7 +25099,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead PCCC</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -25162,7 +25162,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead PCCC</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -25225,7 +25225,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead PCCC</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -25288,7 +25288,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead PCCC</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -25351,7 +25351,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead PCCC</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -25414,7 +25414,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead PCCC</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -25477,7 +25477,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead PCCC</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -25540,7 +25540,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead PCCC</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -25603,7 +25603,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead PCCC</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -25666,7 +25666,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead PCCC</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -25729,7 +25729,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead PCCC</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -25792,7 +25792,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead PCCC</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -25855,7 +25855,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead PCCC</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -25918,7 +25918,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead PCCC</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -25981,7 +25981,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead PCCC</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -26044,7 +26044,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead PCCC</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -26107,7 +26107,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead PCCC</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -26170,7 +26170,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Nhân sự F</t>
+          <t>Lead PCCC</t>
         </is>
       </c>
       <c r="E116" t="n">

--- a/BIM_TK_PowerBI_DataModel_2026.xlsx
+++ b/BIM_TK_PowerBI_DataModel_2026.xlsx
@@ -30482,7 +30482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N215"/>
+  <dimension ref="A1:N152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30565,12 +30565,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 01</t>
+          <t>Dự Án Mẫu MEGA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -30617,12 +30617,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 01</t>
+          <t>Dự Án Mẫu MEGA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -30669,12 +30669,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 01</t>
+          <t>Dự Án Mẫu MEGA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -30721,12 +30721,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 01</t>
+          <t>Dự Án Mẫu MEGA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -30773,12 +30773,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 01</t>
+          <t>Dự Án Mẫu MEGA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -30825,12 +30825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 01</t>
+          <t>Dự Án Mẫu MEGA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -30877,12 +30877,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 01</t>
+          <t>Dự Án Mẫu MEGA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -30929,12 +30929,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 01</t>
+          <t>Dự Án Mẫu MEGA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -30981,12 +30981,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 01</t>
+          <t>Dự Án Mẫu MEGA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -31033,12 +31033,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 01</t>
+          <t>Dự Án Mẫu MEGA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -31085,12 +31085,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 01</t>
+          <t>Dự Án Mẫu MEGA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -31137,12 +31137,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 01</t>
+          <t>Dự Án Mẫu MEGA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -31189,12 +31189,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 01</t>
+          <t>Dự Án Mẫu MEGA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -31241,12 +31241,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 01</t>
+          <t>Dự Án Mẫu MEGA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -31293,12 +31293,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 01</t>
+          <t>Dự Án Mẫu MEGA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 01</t>
+          <t>Dự Án Mẫu MEGA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -31397,12 +31397,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 01</t>
+          <t>Dự Án Mẫu MEGA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -31449,12 +31449,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 01</t>
+          <t>Dự Án Mẫu MEGA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -31501,12 +31501,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 01</t>
+          <t>Dự Án Mẫu MEGA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -31553,12 +31553,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 01</t>
+          <t>Dự Án Mẫu MEGA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -31605,12 +31605,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 01</t>
+          <t>Dự Án Mẫu MEGA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -31657,12 +31657,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 01</t>
+          <t>Dự Án Mẫu MEGA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -31709,12 +31709,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 01</t>
+          <t>Dự Án Mẫu MEGA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -31757,12 +31757,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 01</t>
+          <t>Dự Án Mẫu MEGA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -31806,12 +31806,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 04</t>
+          <t>Hoạch định tổ chức</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D phần mái phục vụ phối hợp va chạm khu nhà điều hành (Dự Án Mẫu 03)</t>
+          <t>Triển khai tài liệu chiến lược, mục tiêu, mô tả công việc cho các chủ trì thiết kế</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -31831,12 +31831,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -31858,12 +31858,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 04</t>
+          <t>Hoạch định tổ chức</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ BTCT sàn mái khu nhà điều hành (Dự Án Mẫu 03)</t>
+          <t>Triển khai tài liệu chi tiết các nhiệm vụ cụ thể cho từng chủ trì để xây dựng hệ thống cho nhóm thiết kế</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -31878,7 +31878,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -31910,17 +31910,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 04</t>
+          <t>Hoạch định tổ chức</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ BTCT sàn mái khu nhà điều hành (Dự Án Mẫu 03)</t>
+          <t>Kế hoạch tuyển dụng nhân sự mới để đủ vân hành bộ máy và thay thế nhân sự đã xin nghỉ</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -31930,17 +31930,13 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -31962,12 +31958,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 04</t>
+          <t>Hoạch định tổ chức</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Trao đổi làm rõ thiếu xót thông tin thiết kế dầm, sàn mái, tập hợp soạn RFI nếu cần</t>
+          <t>Phối hợp HCNS sắp xếp lại, bổ sung bàn làm việc tương ứng với kê hoạch nhân sự</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -31982,7 +31978,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -32014,17 +32010,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 04</t>
+          <t>Hoạch định tổ chức</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ BTCT dầm mái khu nhà điều hành (Dự Án Mẫu 03)</t>
+          <t>Thiết kế cấu trúc dữ liệu hệ thống cho các phòng ban trọng yếu</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -32034,19 +32030,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -32061,22 +32049,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 04</t>
+          <t>Kiến Trúc</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ dầm BTCT tầng mái khu nhà điều hành (Dự Án Mẫu 03)</t>
+          <t>Phân loại hạng mục công trình công ty và mã kí hiệu</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -32086,19 +32074,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -32113,22 +32093,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 04</t>
+          <t>Kiến Trúc</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Thực hiện điều chỉnh bộ bản vẽ dầm tầng mái khu nhà xưởng B (Dự Án Mẫu 04) lần 1</t>
+          <t>Thuyết minh thiết kế quy hoạch, kiến trúc</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -32138,19 +32118,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -32165,22 +32137,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 04</t>
+          <t>Kiến Trúc</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Thực hiện điều chỉnh bộ bản vẽ thang bộ tầng mái khu nhà xưởng A (Dự Án Mẫu 04) lần 2</t>
+          <t>Quy định đặt tên file, mã bản vẽ, tên family, tham biến…</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -32193,16 +32165,8 @@
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -32217,22 +32181,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 04</t>
+          <t>Kiến Trúc</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Thực hiện mô hình 3D tường xây khu nhà xưởng B (Dự Án Mẫu 04) (bao gồm lanh tô, bổ trụ, giằng tường, cửa) để phối hợp va chạm</t>
+          <t>Quy định đặt tên và mã không gian kiến trúc</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -32242,19 +32206,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -32269,22 +32225,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 04</t>
+          <t>Kiến Trúc</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ Shop xây tô tầng 1 khu nhà xưởng B (Dự Án Mẫu 04)</t>
+          <t>Biểu mẫu câu hỏi kiến trúc làm rõ thông tin đầu vào dự án</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -32294,19 +32250,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
@@ -32321,22 +32269,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 04</t>
+          <t>Kiến Trúc</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Trao đổi làm rõ thiếu xót thông tin thiết kế tường xây, tập hợp soạn RFI nếu cần</t>
+          <t>Check list danh mục hồ sơ thông tin đầu vào dự án để triển khai thiết kế kiến trúc từng giai đoạn</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -32346,19 +32294,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
@@ -32373,22 +32313,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 04</t>
+          <t>Kiến Trúc</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ shop đấu nối nước mưa, nước thải theo chỉ thị phát sinh công trường</t>
+          <t>Danh mục vật liệu hoàn thiện kèm mã vật liệu, đặc tả kĩ thuật đi kèm</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -32398,19 +32338,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
@@ -32425,22 +32357,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 02</t>
+          <t>Kiến Trúc</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tính và cấp khối lượng thép bổ sung cho đường đấu nối</t>
+          <t>Template (Autocad) bao gồm chi tiết điển hình kiến trúc, các lớp cấu tạo hoàn thiện đã chuẩn hoá</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -32450,19 +32382,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
@@ -32477,22 +32401,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 02</t>
+          <t>Kiến Trúc</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Trao đổi làm rõ thiếu xót thông tin thiết kế ramp, tập hợp soạn RFI</t>
+          <t>Biểu mẫu lập tiến độ thiết kế kiến trúc</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -32502,19 +32426,11 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
@@ -32529,22 +32445,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 02</t>
+          <t>Kiến Trúc</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Điều chỉnh bản vẽ sàn desking do vẽ thiếu</t>
+          <t>Danh mục bản vẽ thiết kế kiến trúc (tên và mã)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -32554,19 +32470,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
@@ -32581,22 +32489,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 02</t>
+          <t>Kiến Trúc</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Điều chỉnh bản vẽ shop do điều chỉnh cao độ nhà bảo vệ theo yêu cầu BCH, CĐT</t>
+          <t>Quy trình thiết kế kiến trúc theo giai đoạn</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -32606,19 +32514,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
@@ -32633,17 +32533,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 02</t>
+          <t>Kiến Trúc</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Điều chỉnh bản vẽ Shop hàng rào do yêu cầu điều chỉnh cao độ thiết kế phù hợp thực tế</t>
+          <t>Quy trình điều chỉnh thiết kế</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -32658,15 +32558,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
@@ -32681,17 +32577,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 02</t>
+          <t>Kiến Trúc</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Phối hợp soạn và cấp thông tin khối lương, mô hình, bản vẽ phục vụ hồ sơ nghiệm thu IPC (Dự Án Mẫu 05)</t>
+          <t>Biểu mẫu tính toán phục vụ thiết kế kiến trúc</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -32706,7 +32602,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -32725,22 +32621,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 02</t>
+          <t>Kiến Trúc</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D ốp lát hoàn thiện khu văn phòng, phối hợp xây tô, kết cấu thép, cửa...</t>
+          <t>Template triển khai thiết kế kiến trúc (Revit)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -32750,19 +32646,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -32777,17 +32665,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 02</t>
+          <t>Kiến Trúc</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ Shop hoàn thiện ốp lát khu văn phòng xưởng (Dự Án Mẫu 01)</t>
+          <t>Hướng dẫn triển khai bản vẽ trên các Template Revit, CAD</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -32802,15 +32690,11 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
@@ -32825,22 +32709,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 02</t>
+          <t>Kiến Trúc</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng gạch ốp lát khu văn phòng xưởng (Dự Án Mẫu 01)</t>
+          <t>Công cụ tự động hoá kèm danh mục phcuj vụ triển khai thiết kế kiến trúc</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -32850,19 +32734,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
@@ -32877,22 +32753,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 02</t>
+          <t>Kiến Trúc</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D ốp lát hoàn thiện khu vệ sinh (Dự Án Mẫu 01)</t>
+          <t>Tài liệu tập hợp các lỗi hay gặp trong thiết kế kiến trúc các hạng mục</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -32902,19 +32778,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
@@ -32929,17 +32797,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 02</t>
+          <t>Kiến Trúc</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ Shop hoàn thiện ốp lát khu vệ sinh (Dự Án Mẫu 01)</t>
+          <t>Check list kiểm tra chất lượng thiết kế kiến trúc theo hạng mục</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -32954,15 +32822,11 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
@@ -32977,22 +32841,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 02</t>
+          <t>Kiến Trúc</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng gạch ốp lát khu vệ sinh (Dự Án Mẫu 01)</t>
+          <t>Chuẩn hoá thiết kế kiến trúc các hạng mục</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -33002,19 +32866,11 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -33029,22 +32885,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 02</t>
+          <t>Kiến Trúc</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D ốp lát hoàn thiện nhà bảo vệ (Dự Án Mẫu 01)</t>
+          <t>BOQ chuẩn hoá kiến trúc</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -33054,19 +32910,11 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
@@ -33081,17 +32929,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 02</t>
+          <t>Kết cấu</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ Shop hoàn thiện ốp lát nhà bảo vệ (Dự Án Mẫu 01)</t>
+          <t>Biểu mẫu ghi chú chung cho kết cấu</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -33106,15 +32954,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
@@ -33129,22 +32973,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 02</t>
+          <t>Kết cấu</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng gạch ốp lát nhà bảo vệ (Dự Án Mẫu 01)</t>
+          <t>Thuyết minh thiết kế kết cấu, chỉ dẫn kĩ thuật</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -33154,19 +32998,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
@@ -33181,17 +33017,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 02</t>
+          <t>Kết cấu</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Thực hiện bổ sung bản vẽ đấu nối theo yêu cầu CĐT, BCH</t>
+          <t>Quy định đặt tên file, mã bản vẽ, tên family, tham biến kết cấu…</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -33210,11 +33046,7 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
@@ -33229,22 +33061,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 02</t>
+          <t>Kết cấu</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ Shop sàn nóc thang</t>
+          <t>Quy định đặt tên cấu kiện kết cấu</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -33257,16 +33089,8 @@
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
@@ -33281,22 +33105,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 02</t>
+          <t>Kết cấu</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Điều chỉnh và phát hành mô hình 3D cho tất cả các thay đổi thiết kế dự án mẫu</t>
+          <t>Quy định về hệ số an toàn khi thiết kế kết cấu cho từng loại cấu kiện</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -33306,19 +33130,11 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
@@ -33333,22 +33149,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 03</t>
+          <t>Kết cấu</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D phần phục vụ phối hợp va chạm nhà phụ trợ kỹ thuật (Dự Án Mẫu 01) (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
+          <t>Biểu mẫu câu hỏi kết cấu làm rõ thông tin đầu vào khi triển khai dự án</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -33358,19 +33174,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
@@ -33385,22 +33193,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 03</t>
+          <t>Kết cấu</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ Shop đà kiềng và nền bể chứa và bể XLNT nhà phụ trợ kỹ thuật (Dự Án Mẫu 01)</t>
+          <t>Check list danh mục hồ sơ thông tin đầu vào triển khai phương án thiết kế kết cấu dự án</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -33410,19 +33218,11 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
@@ -33437,17 +33237,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 03</t>
+          <t>Kết cấu</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng bê tông, cốt thép, ván khuôn và các khối lượng xuất từ bản vẽ đà kiềng và nền nhà phụ trợ kỹ thuật (Dự Án Mẫu 01)</t>
+          <t>Danh mục vật liệu,vật tư kèm mã vật liệu, vật tư phần kết cấu</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -33462,7 +33262,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
@@ -33481,22 +33281,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 03</t>
+          <t>Kết cấu</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D phần hạ tầng điện (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
+          <t>Template (Autocad) bao gồm chi tiết điển hình kết cấu, các lớp cấu tạo hoàn thiện đã chuẩn hoá</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -33506,19 +33306,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
@@ -33533,22 +33325,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 03</t>
+          <t>Kết cấu</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D phần hạ tầng cấp nước (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
+          <t>Biểu mẫu lập tiến độ thiết kế kết cấu</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -33558,19 +33350,11 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
@@ -33585,22 +33369,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 03</t>
+          <t>Kết cấu</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D phần hạ tầng PCCC (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
+          <t>Danh mục bản vẽ kết cấu (tên và mã)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -33610,19 +33394,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
@@ -33637,17 +33413,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 03</t>
+          <t>Kết cấu</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Thực hiện điều chỉnh mô hình 3D phối hợp hạ tầng cho tất cả các bộ môn (Nước mưa, nước thải, điện, cấp thoát nước, PCCC...)</t>
+          <t>Quy trình thiết kế tổng thể và chi tiết kết cấu theo từng hạng mục</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -33666,11 +33442,7 @@
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
@@ -33685,17 +33457,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 03</t>
+          <t>Kết cấu</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng đào đào đắp</t>
+          <t>Quy trình điều chỉnh thiết kế kết cấu</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -33710,7 +33482,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -33729,17 +33501,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 03</t>
+          <t>Kết cấu</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng hệ thống nước mưa</t>
+          <t>Template mô hình tính toán SAP, Etab…</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -33754,7 +33526,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -33773,17 +33545,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 03</t>
+          <t>Kết cấu</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng hệ thống nước thải</t>
+          <t>Bảng tính mẫu dùng để kiểm tra, tính toán kết cấu</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -33798,7 +33570,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
@@ -33817,17 +33589,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 03</t>
+          <t>Kết cấu</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng hệ thống cấp thoát nước hạ tầng</t>
+          <t>Template triển khai thiết kế kết cấu (Revit)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -33842,7 +33614,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -33861,17 +33633,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 03</t>
+          <t>Kết cấu</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng hệ thống phòng cháy chữa cháy</t>
+          <t>Hướng dẫn triển khai bản vẽ kết cấu trên cácTemplate</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -33886,7 +33658,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
@@ -33905,17 +33677,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 03</t>
+          <t>Kết cấu</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lương hệ thống điện hạ tầng</t>
+          <t>Công cụ tự động hoá kèm danh mục</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -33930,7 +33702,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -33949,17 +33721,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 03</t>
+          <t>Kết cấu</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Kiểm soát thiết kế kết cấu thép cụm nhà xưởng mở rộng (Dự Án Mẫu 01)</t>
+          <t>Tài liệu tập hợp các lỗi hay gặp trong thiết kế kết cấu các hạng mục</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -33974,7 +33746,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -33993,17 +33765,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 03</t>
+          <t>Kết cấu</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Kiểm soát thiết kế kết cấu thép cụm nhà xưởng sản xuất chính (Dự Án Mẫu 01) cùng Đơn vị gia công kết cấu thép</t>
+          <t>Chuẩn hoá thiết kế kết cấu các hạng mục</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -34018,7 +33790,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -34037,22 +33809,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 05</t>
+          <t>Kết cấu</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Triẻn khai mô hình 3D phục vụ phối hợp va chạm phần ngầm bể tự hoại (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý) (tách 2 gói)</t>
+          <t>BOQ chuẩn hoá kết cấu</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -34062,19 +33834,11 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>01/04</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
@@ -34089,22 +33853,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 05</t>
+          <t>Kết cấu</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ Shop bể tự hoại theo phương án đúc trên bãi (tách 2 bộ bản vẽ 2 gói)</t>
+          <t>Biện pháp thi công định hướng</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -34114,19 +33878,11 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>03/04</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
@@ -34141,22 +33897,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 05</t>
+          <t>Kết cấu</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng bê tông, cốt thép bể tự hoại (tách 2 bộ cho 2 gói)</t>
+          <t>Các biểu mẫu so sánh giữa các phương án thiết kế</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -34166,19 +33922,11 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>10/04</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
@@ -34193,22 +33941,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 05</t>
+          <t>Hệ thống điện</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Thực hiện điều chỉnh bản vẽ bể tự hoại lần 1 (tách 2 bộ cho 2 gói)</t>
+          <t>Thuyết minh thiết kế hệ thống điện, chỉ dẫn kĩ thuật</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -34218,19 +33966,11 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>06/04</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
@@ -34245,22 +33985,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 05</t>
+          <t>Hệ thống điện</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Thực hiện điều chỉnh bản vẽ Shop móng và cổ cột các phân đoạn móng (Dự Án Mẫu 07) theo yêu cầu BCH (tách gói, chạy tọa độ)</t>
+          <t>Quy định đặt tên file, mã bản vẽ, tên family, tham biến…</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -34270,19 +34010,11 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>06/04</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
@@ -34297,22 +34029,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 05</t>
+          <t>Hệ thống điện</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng bê tông, cốt thép móng và cổ cột cho các phân đoạn móng (Dự Án Mẫu 07)</t>
+          <t>Các bảng tính thiết kế hệ thống điện</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -34322,19 +34054,11 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>07/04</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
@@ -34349,22 +34073,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 05</t>
+          <t>Hệ thống điện</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Thực hiện triển khai tính toán khối lượng san lấp theo yêu cầu BCH</t>
+          <t>Biểu mẫu câu hỏi làm rõ thông tin kĩ thuật đầu vào khi triển khai dự án</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -34374,19 +34098,11 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>07/04</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
@@ -34401,17 +34117,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 05</t>
+          <t>Hệ thống điện</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Thực hiện điều chỉnh bản vẽ Shop móng và cổ cột các phân đoạn móng (Dự Án Mẫu 07) theo comments TVGS lần 1</t>
+          <t>Check list danh mục hồ sơ thông tin đầu vào triển khai phương án thiết kế điện dự án</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -34426,15 +34142,11 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>06/04</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
@@ -34449,17 +34161,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 05</t>
+          <t>Hệ thống điện</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D phần hạ tầng đường, cảnh quan phục vụ phối hợp va chạm</t>
+          <t>Danh mục vật tư, thiết bị kèm mã</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -34474,15 +34186,11 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
@@ -34497,22 +34205,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 06</t>
+          <t>Hệ thống điện</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D xây tô nhà trạm kỹ thuật (Dự Án Mẫu 06) (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
+          <t>Template (Autocad) bao gồm chi tiết lắp đặt điển hình của hệ thống điện</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -34522,19 +34230,11 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
@@ -34549,22 +34249,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 06</t>
+          <t>Hệ thống điện</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ shop xây tô nhà trạm kỹ thuật (Dự Án Mẫu 06)</t>
+          <t>Biểu mẫu lập tiến độ thiết kế hệ thống điện</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -34574,19 +34274,11 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
@@ -34601,22 +34293,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 06</t>
+          <t>Hệ thống điện</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng xây tô nhà trạm kỹ thuật (Dự Án Mẫu 06)</t>
+          <t>Danh mục bản vẽ (tên và mã)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -34626,19 +34318,11 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
@@ -34653,22 +34337,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 06</t>
+          <t>Hệ thống điện</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Triển khai mô hình 3D ốp lát nhà vệ sinh trạm nguồn điện kỹ thuật (Dự Án Mẫu 06) (phát hiện lỗi, báo cáo, đề xuất phương án, trao đổi các bên xử lý)</t>
+          <t>Quy trình thiết kế tổng thể và chi tiết theo từng hạng mục</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -34678,19 +34362,11 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
@@ -34705,22 +34381,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 06</t>
+          <t>Hệ thống điện</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Triển khai bản vẽ shop ốp lát nhà vệ sinh trạm nguồn điện kỹ thuật (Dự Án Mẫu 06)</t>
+          <t>Các sơ đồ nguyên lý điển hình (Autocad)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -34730,19 +34406,11 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
@@ -34757,22 +34425,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 06</t>
+          <t>Hệ thống điện</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Triển khai các bảng khối lượng ốp lát trạm nguồn điện kỹ thuật (Dự Án Mẫu 06)</t>
+          <t>Template triển khai thiết kế Điện (Revit)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -34782,19 +34450,11 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
@@ -34809,22 +34469,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 06</t>
+          <t>Hệ thống điện</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Triển khai bảng khối lượng chi tiết trạm nguồn điện kỹ thuật (Dự Án Mẫu 06) phục vụ hồ sơ nghiệm thu IPC (Dự Án Mẫu 05)</t>
+          <t>Hướng dẫn triển khai bản vẽ trên cácTemplate</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Quá hạn</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -34834,19 +34494,11 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
@@ -34861,22 +34513,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 07</t>
+          <t>Hệ thống điện</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Kiểm tra khối lượng phát sinh thép gia cường chân cột, xác định nguyên nhân, đặt hàng bổ sung theo thực tế triển khai</t>
+          <t>Bộ công cụ tự động hoá kèm danh mục</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -34889,16 +34541,8 @@
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
@@ -34913,22 +34557,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu 07</t>
+          <t>Hệ thống điện</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Thực hiện điều chỉnh bản vẽ Shop ron nhà để xe theo yêu cầu bổ sung BCH</t>
+          <t>Tài liệu tập hợp các lỗi hay gặp trong thiết kế điện các hạng mục</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -34938,19 +34582,11 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
@@ -34965,22 +34601,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Hoạch định tổ chức</t>
+          <t>Hệ thống điện</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Triển khai tài liệu chiến lược, mục tiêu, mô tả công việc cho các chủ trì thiết kế</t>
+          <t>Chuẩn hoá thiết kế các hạng mục</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -34990,19 +34626,11 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
@@ -35017,22 +34645,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hoạch định tổ chức</t>
+          <t>Hệ thống điện</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Triển khai tài liệu chi tiết các nhiệm vụ cụ thể cho từng chủ trì để xây dựng hệ thống cho nhóm thiết kế</t>
+          <t>BOQ chuẩn hoá hệ thống điện</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -35042,19 +34670,11 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
@@ -35069,17 +34689,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hoạch định tổ chức</t>
+          <t>Hệ thống điện</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Kế hoạch tuyển dụng nhân sự mới để đủ vân hành bộ máy và thay thế nhân sự đã xin nghỉ</t>
+          <t>Các biểu mẫu so sánh giữa các phương án thiết kế hệ thống điện</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -35098,11 +34718,7 @@
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
@@ -35117,22 +34733,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hoạch định tổ chức</t>
+          <t>Điều hoà thông gió</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Phối hợp HCNS sắp xếp lại, bổ sung bàn làm việc tương ứng với kê hoạch nhân sự</t>
+          <t>Thuyết minh thiết kế hệ thống điều hoà thông gió, chỉ dẫn kĩ thuật</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Đang thực hiện</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -35142,19 +34758,11 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
@@ -35169,17 +34777,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Quản trị &amp; Tổ chức</t>
+          <t>Chuẩn hóa Bộ môn Thiết kế</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hoạch định tổ chức</t>
+          <t>Điều hoà thông gió</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Thiết kế cấu trúc dữ liệu hệ thống cho các phòng ban trọng yếu</t>
+          <t>Quy định đặt tên file, mã bản vẽ, tên family, tham biến…</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -35194,7 +34802,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -35218,12 +34826,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kiến Trúc</t>
+          <t>Điều hoà thông gió</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Phân loại hạng mục công trình công ty và mã kí hiệu</t>
+          <t>Các bảng tính thiết kế HVAC</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -35262,12 +34870,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Kiến Trúc</t>
+          <t>Điều hoà thông gió</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Thuyết minh thiết kế quy hoạch, kiến trúc</t>
+          <t>Biểu mẫu câu hỏi làm rõ thông tin kĩ thuật đầu vào khi triển khai dự án</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -35306,12 +34914,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Kiến Trúc</t>
+          <t>Điều hoà thông gió</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Quy định đặt tên file, mã bản vẽ, tên family, tham biến…</t>
+          <t>Check list danh mục hồ sơ thông tin đầu vào triển khai thiết kế HVAC dự án</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -35350,12 +34958,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Kiến Trúc</t>
+          <t>Điều hoà thông gió</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Quy định đặt tên và mã không gian kiến trúc</t>
+          <t>Danh mục vật tư, thiết bị kèm mã, quy cách kĩ thuật</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -35394,12 +35002,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Kiến Trúc</t>
+          <t>Điều hoà thông gió</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Biểu mẫu câu hỏi kiến trúc làm rõ thông tin đầu vào dự án</t>
+          <t>Template (Autocad) bao gồm chi tiết lắp đặt điển hình HVAC</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -35438,12 +35046,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Kiến Trúc</t>
+          <t>Điều hoà thông gió</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Check list danh mục hồ sơ thông tin đầu vào dự án để triển khai thiết kế kiến trúc từng giai đoạn</t>
+          <t>Biểu mẫu lập tiến độ thiết kế HVAC</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -35482,12 +35090,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Kiến Trúc</t>
+          <t>Điều hoà thông gió</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Danh mục vật liệu hoàn thiện kèm mã vật liệu, đặc tả kĩ thuật đi kèm</t>
+          <t>Danh mục bản vẽ (tên và mã) HVAC</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -35526,12 +35134,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Kiến Trúc</t>
+          <t>Điều hoà thông gió</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Template (Autocad) bao gồm chi tiết điển hình kiến trúc, các lớp cấu tạo hoàn thiện đã chuẩn hoá</t>
+          <t>Quy trình thiết kế tổng thể và chi tiết theo từng hạng mục</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -35570,12 +35178,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Kiến Trúc</t>
+          <t>Điều hoà thông gió</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Biểu mẫu lập tiến độ thiết kế kiến trúc</t>
+          <t>Các sơ đồ nguyên lý điển hình (Autocad) HVAC</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -35614,12 +35222,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Kiến Trúc</t>
+          <t>Điều hoà thông gió</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Danh mục bản vẽ thiết kế kiến trúc (tên và mã)</t>
+          <t>Template triển khai thiết kế HVAC (Revit)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -35658,12 +35266,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Kiến Trúc</t>
+          <t>Điều hoà thông gió</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Quy trình thiết kế kiến trúc theo giai đoạn</t>
+          <t>Hướng dẫn triển khai bản vẽ trên cácTemplate</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -35702,12 +35310,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Kiến Trúc</t>
+          <t>Điều hoà thông gió</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Quy trình điều chỉnh thiết kế</t>
+          <t>Bộ công cụ tự động hoá kèm danh mục hệ thống HVAC</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -35746,12 +35354,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Kiến Trúc</t>
+          <t>Điều hoà thông gió</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Biểu mẫu tính toán phục vụ thiết kế kiến trúc</t>
+          <t>Tài liệu tập hợp các lỗi hay gặp trong thiết kế HVAC các hạng mục</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -35790,12 +35398,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Kiến Trúc</t>
+          <t>Điều hoà thông gió</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Template triển khai thiết kế kiến trúc (Revit)</t>
+          <t>Chuẩn hoá thiết kế các hạng mục HVAC</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -35834,12 +35442,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Kiến Trúc</t>
+          <t>Điều hoà thông gió</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Hướng dẫn triển khai bản vẽ trên các Template Revit, CAD</t>
+          <t>BOQ chuẩn hoá HVAC</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -35878,12 +35486,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Kiến Trúc</t>
+          <t>Điều hoà thông gió</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Công cụ tự động hoá kèm danh mục phcuj vụ triển khai thiết kế kiến trúc</t>
+          <t>Các biểu mẫu so sánh giữa các phương án thiết kế HVAC</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -35922,12 +35530,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Kiến Trúc</t>
+          <t>Cấp thoát nước</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Tài liệu tập hợp các lỗi hay gặp trong thiết kế kiến trúc các hạng mục</t>
+          <t>Thuyết minh thiết kế hệ thống CTN, chỉ dẫn kĩ thuật</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -35966,12 +35574,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Kiến Trúc</t>
+          <t>Cấp thoát nước</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Check list kiểm tra chất lượng thiết kế kiến trúc theo hạng mục</t>
+          <t>Quy định đặt tên file, mã bản vẽ, tên family, tham biến…</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -36010,12 +35618,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Kiến Trúc</t>
+          <t>Cấp thoát nước</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Chuẩn hoá thiết kế kiến trúc các hạng mục</t>
+          <t>Các bảng tính thiết kế hệ thống CTN</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -36054,12 +35662,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Kiến Trúc</t>
+          <t>Cấp thoát nước</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>BOQ chuẩn hoá kiến trúc</t>
+          <t>Biểu mẫu câu hỏi làm rõ thông tin kĩ thuật đầu vào khi triển khai dự án</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -36098,12 +35706,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Kết cấu</t>
+          <t>Cấp thoát nước</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Biểu mẫu ghi chú chung cho kết cấu</t>
+          <t>Check list danh mục hồ sơ thông tin đầu vào triển khai phương án thiết kế CTN dự án</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -36142,12 +35750,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Kết cấu</t>
+          <t>Cấp thoát nước</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Thuyết minh thiết kế kết cấu, chỉ dẫn kĩ thuật</t>
+          <t>Danh mục vật tư, thiết bị kèm mã</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -36186,12 +35794,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Kết cấu</t>
+          <t>Cấp thoát nước</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Quy định đặt tên file, mã bản vẽ, tên family, tham biến kết cấu…</t>
+          <t>Template (Autocad) bao gồm chi tiết lắp đặt điển hình của hệ thống CTN</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -36230,12 +35838,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Kết cấu</t>
+          <t>Cấp thoát nước</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Quy định đặt tên cấu kiện kết cấu</t>
+          <t>Biểu mẫu lập tiến độ thiết kế hệ thống CTN</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -36274,12 +35882,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Kết cấu</t>
+          <t>Cấp thoát nước</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Quy định về hệ số an toàn khi thiết kế kết cấu cho từng loại cấu kiện</t>
+          <t>Danh mục bản vẽ (tên và mã) hệ thống cấp thoát nước</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -36318,12 +35926,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Kết cấu</t>
+          <t>Cấp thoát nước</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Biểu mẫu câu hỏi kết cấu làm rõ thông tin đầu vào khi triển khai dự án</t>
+          <t>Quy trình thiết kế tổng thể và chi tiết theo từng hạng mục</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -36362,12 +35970,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Kết cấu</t>
+          <t>Cấp thoát nước</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Check list danh mục hồ sơ thông tin đầu vào triển khai phương án thiết kế kết cấu dự án</t>
+          <t>Các sơ đồ nguyên lý điển hình CTN</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -36406,12 +36014,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Kết cấu</t>
+          <t>Cấp thoát nước</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Danh mục vật liệu,vật tư kèm mã vật liệu, vật tư phần kết cấu</t>
+          <t>Template triển khai thiết kế CTN (Revit)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -36450,12 +36058,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Kết cấu</t>
+          <t>Cấp thoát nước</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Template (Autocad) bao gồm chi tiết điển hình kết cấu, các lớp cấu tạo hoàn thiện đã chuẩn hoá</t>
+          <t>Hướng dẫn triển khai bản vẽ trên cácTemplate</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -36494,12 +36102,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Kết cấu</t>
+          <t>Cấp thoát nước</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Biểu mẫu lập tiến độ thiết kế kết cấu</t>
+          <t>Bộ công cụ tự động hoá kèm danh mục cho hệ thống cấp thoát nước</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -36538,12 +36146,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Kết cấu</t>
+          <t>Cấp thoát nước</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Danh mục bản vẽ kết cấu (tên và mã)</t>
+          <t>Tài liệu tập hợp các lỗi hay gặp trong thiết kế CTN các hạng mục</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -36582,12 +36190,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Kết cấu</t>
+          <t>Cấp thoát nước</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Quy trình thiết kế tổng thể và chi tiết kết cấu theo từng hạng mục</t>
+          <t>Chuẩn hoá thiết kế các hạng mục</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -36626,12 +36234,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Kết cấu</t>
+          <t>Cấp thoát nước</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Quy trình điều chỉnh thiết kế kết cấu</t>
+          <t>BOQ chuẩn hoá hệ thống cấp thoát nước</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -36670,12 +36278,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Kết cấu</t>
+          <t>Cấp thoát nước</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Template mô hình tính toán SAP, Etab…</t>
+          <t>Các biểu mẫu so sánh giữa các phương án thiết kế CTN</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -36714,12 +36322,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Kết cấu</t>
+          <t>Phòng cháy chữa cháy</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Bảng tính mẫu dùng để kiểm tra, tính toán kết cấu</t>
+          <t>Thuyết minh thiết kế hệ thống PCCC, chỉ dẫn kĩ thuật</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -36758,12 +36366,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Kết cấu</t>
+          <t>Phòng cháy chữa cháy</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Template triển khai thiết kế kết cấu (Revit)</t>
+          <t>Quy định đặt tên file, mã bản vẽ, tên family, tham biến…hệ thống PCCC</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -36802,12 +36410,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Kết cấu</t>
+          <t>Phòng cháy chữa cháy</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Hướng dẫn triển khai bản vẽ kết cấu trên cácTemplate</t>
+          <t>Các bảng tính thiết kế hệ thống PCCC</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -36846,12 +36454,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Kết cấu</t>
+          <t>Phòng cháy chữa cháy</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Công cụ tự động hoá kèm danh mục</t>
+          <t>Biểu mẫu câu hỏi làm rõ thông tin kĩ thuật đầu vào khi triển khai dự án</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -36890,12 +36498,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Kết cấu</t>
+          <t>Phòng cháy chữa cháy</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Tài liệu tập hợp các lỗi hay gặp trong thiết kế kết cấu các hạng mục</t>
+          <t>Check list danh mục hồ sơ thông tin đầu vào triển khai phương án thiết kế PCCC dự án</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -36934,12 +36542,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Kết cấu</t>
+          <t>Phòng cháy chữa cháy</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Chuẩn hoá thiết kế kết cấu các hạng mục</t>
+          <t>Danh mục vật tư, thiết bị kèm mã hệ thống PCCC</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -36978,12 +36586,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Kết cấu</t>
+          <t>Phòng cháy chữa cháy</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>BOQ chuẩn hoá kết cấu</t>
+          <t>Template (Autocad) bao gồm chi tiết lắp đặt điển hình của hệ thống PCCC</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -37022,12 +36630,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Kết cấu</t>
+          <t>Phòng cháy chữa cháy</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Biện pháp thi công định hướng</t>
+          <t>Biểu mẫu lập tiến độ thiết kế hệ thống PCCC</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -37066,12 +36674,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Kết cấu</t>
+          <t>Phòng cháy chữa cháy</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Các biểu mẫu so sánh giữa các phương án thiết kế</t>
+          <t>Danh mục bản vẽ (tên và mã) hệ thôgns PCCC</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -37110,12 +36718,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Hệ thống điện</t>
+          <t>Phòng cháy chữa cháy</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Thuyết minh thiết kế hệ thống điện, chỉ dẫn kĩ thuật</t>
+          <t>Quy trình thiết kế tổng thể và chi tiết theo từng hạng mục</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -37154,12 +36762,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Hệ thống điện</t>
+          <t>Phòng cháy chữa cháy</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Quy định đặt tên file, mã bản vẽ, tên family, tham biến…</t>
+          <t>Các sơ đồ nguyên lý điển hình PCCC</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -37198,12 +36806,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Hệ thống điện</t>
+          <t>Phòng cháy chữa cháy</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Các bảng tính thiết kế hệ thống điện</t>
+          <t>Template triển khai thiết kế PCCC (Revit)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -37242,12 +36850,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Hệ thống điện</t>
+          <t>Phòng cháy chữa cháy</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Biểu mẫu câu hỏi làm rõ thông tin kĩ thuật đầu vào khi triển khai dự án</t>
+          <t>Hướng dẫn triển khai bản vẽ trên cácTemplate PCCC</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -37286,12 +36894,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Hệ thống điện</t>
+          <t>Phòng cháy chữa cháy</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Check list danh mục hồ sơ thông tin đầu vào triển khai phương án thiết kế điện dự án</t>
+          <t>Bộ công cụ tự động hoá kèm danh mục hệ thống PCCC</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -37330,12 +36938,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Hệ thống điện</t>
+          <t>Phòng cháy chữa cháy</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Danh mục vật tư, thiết bị kèm mã</t>
+          <t>Tài liệu tập hợp các lỗi hay gặp trong thiết kế PCCC các hạng mục</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -37374,12 +36982,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Hệ thống điện</t>
+          <t>Phòng cháy chữa cháy</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Template (Autocad) bao gồm chi tiết lắp đặt điển hình của hệ thống điện</t>
+          <t>Chuẩn hoá thiết kế các hạng mục hệ PCCC</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -37418,12 +37026,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Hệ thống điện</t>
+          <t>Phòng cháy chữa cháy</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Biểu mẫu lập tiến độ thiết kế hệ thống điện</t>
+          <t>BOQ chuẩn hoá hệ PCCC</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -37462,12 +37070,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Hệ thống điện</t>
+          <t>Phòng cháy chữa cháy</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Danh mục bản vẽ (tên và mã)</t>
+          <t>Các biểu mẫu so sánh giữa các phương án thiết kế PCCC</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -37501,17 +37109,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Hệ thống điện</t>
+          <t>Đào tạo phát triển</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Quy trình thiết kế tổng thể và chi tiết theo từng hạng mục</t>
+          <t>Đào tạo về quản lý dự án với BIM (khoảng 20 buổi)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -37526,11 +37134,15 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
@@ -37545,17 +37157,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Hệ thống điện</t>
+          <t>Đào tạo phát triển</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Các sơ đồ nguyên lý điển hình (Autocad)</t>
+          <t>Đào tạo lập trình, sử dụng công cụ tự động hoá</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -37570,7 +37182,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
@@ -37589,22 +37201,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Hệ thống điện</t>
+          <t>Đào tạo phát triển</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Template triển khai thiết kế Điện (Revit)</t>
+          <t>Đào tạo tư duy hoạch định mục tiêu, kế hoạch</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Đang thực hiện</t>
+          <t>Chưa thực hiện</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -37612,11 +37224,7 @@
           <t>P. BIM</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
@@ -37633,17 +37241,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Hệ thống điện</t>
+          <t>Xây dựng văn hoá</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Hướng dẫn triển khai bản vẽ trên cácTemplate</t>
+          <t>Truyền thông tinh thần làm việc, văn háo học tập, chia sẻ</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -37658,7 +37266,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
@@ -37677,17 +37285,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Hệ thống điện</t>
+          <t>Xây dựng văn hoá</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Bộ công cụ tự động hoá kèm danh mục</t>
+          <t>Tổ chức các hoạt động gắn kết đội nhóm</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -37702,7 +37310,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
@@ -37721,17 +37329,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Hệ thống điện</t>
+          <t>Xây dựng văn hoá</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Tài liệu tập hợp các lỗi hay gặp trong thiết kế điện các hạng mục</t>
+          <t>Trợ lực, đồng hành, cầm tay chỉ việc cho các nhiệm vụ khó khăn</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -37746,7 +37354,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
@@ -37765,17 +37373,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
+          <t>Quản trị &amp; Tổ chức</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Hệ thống điện</t>
+          <t>Xây dựng văn hoá</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Chuẩn hoá thiết kế các hạng mục</t>
+          <t>Định hướng phát triển tương lai, đối thoại thẳng thắn, tôn trọng quyết định người lao động</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -37790,7 +37398,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
@@ -37801,2778 +37409,6 @@
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
     </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>TSK_152</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Hệ thống điện</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>BOQ chuẩn hoá hệ thống điện</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>TSK_153</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Hệ thống điện</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>Các biểu mẫu so sánh giữa các phương án thiết kế hệ thống điện</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>TSK_154</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Điều hoà thông gió</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Thuyết minh thiết kế hệ thống điều hoà thông gió, chỉ dẫn kĩ thuật</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>TSK_155</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Điều hoà thông gió</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Quy định đặt tên file, mã bản vẽ, tên family, tham biến…</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>TSK_156</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Điều hoà thông gió</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Các bảng tính thiết kế HVAC</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>TSK_157</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Điều hoà thông gió</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>Biểu mẫu câu hỏi làm rõ thông tin kĩ thuật đầu vào khi triển khai dự án</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>TSK_158</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Điều hoà thông gió</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Check list danh mục hồ sơ thông tin đầu vào triển khai thiết kế HVAC dự án</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>TSK_159</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Điều hoà thông gió</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>Danh mục vật tư, thiết bị kèm mã, quy cách kĩ thuật</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>TSK_160</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Điều hoà thông gió</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>Template (Autocad) bao gồm chi tiết lắp đặt điển hình HVAC</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr"/>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>TSK_161</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Điều hoà thông gió</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>Biểu mẫu lập tiến độ thiết kế HVAC</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr"/>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>TSK_162</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Điều hoà thông gió</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>Danh mục bản vẽ (tên và mã) HVAC</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr"/>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>TSK_163</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Điều hoà thông gió</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>Quy trình thiết kế tổng thể và chi tiết theo từng hạng mục</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>TSK_164</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Điều hoà thông gió</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>Các sơ đồ nguyên lý điển hình (Autocad) HVAC</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>TSK_165</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Điều hoà thông gió</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>Template triển khai thiết kế HVAC (Revit)</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>TSK_166</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Điều hoà thông gió</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>Hướng dẫn triển khai bản vẽ trên cácTemplate</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>TSK_167</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Điều hoà thông gió</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>Bộ công cụ tự động hoá kèm danh mục hệ thống HVAC</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>TSK_168</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Điều hoà thông gió</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>Tài liệu tập hợp các lỗi hay gặp trong thiết kế HVAC các hạng mục</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>TSK_169</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Điều hoà thông gió</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>Chuẩn hoá thiết kế các hạng mục HVAC</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>TSK_170</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Điều hoà thông gió</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>BOQ chuẩn hoá HVAC</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>TSK_171</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Điều hoà thông gió</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>Các biểu mẫu so sánh giữa các phương án thiết kế HVAC</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>TSK_172</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Cấp thoát nước</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>Thuyết minh thiết kế hệ thống CTN, chỉ dẫn kĩ thuật</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>TSK_173</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Cấp thoát nước</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>Quy định đặt tên file, mã bản vẽ, tên family, tham biến…</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>TSK_174</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Cấp thoát nước</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>Các bảng tính thiết kế hệ thống CTN</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>TSK_175</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Cấp thoát nước</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>Biểu mẫu câu hỏi làm rõ thông tin kĩ thuật đầu vào khi triển khai dự án</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>TSK_176</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Cấp thoát nước</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>Check list danh mục hồ sơ thông tin đầu vào triển khai phương án thiết kế CTN dự án</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>TSK_177</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Cấp thoát nước</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>Danh mục vật tư, thiết bị kèm mã</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>TSK_178</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Cấp thoát nước</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>Template (Autocad) bao gồm chi tiết lắp đặt điển hình của hệ thống CTN</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr"/>
-      <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>TSK_179</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Cấp thoát nước</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>Biểu mẫu lập tiến độ thiết kế hệ thống CTN</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>TSK_180</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Cấp thoát nước</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>Danh mục bản vẽ (tên và mã) hệ thống cấp thoát nước</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr"/>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>TSK_181</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Cấp thoát nước</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>Quy trình thiết kế tổng thể và chi tiết theo từng hạng mục</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>TSK_182</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Cấp thoát nước</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>Các sơ đồ nguyên lý điển hình CTN</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>TSK_183</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Cấp thoát nước</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>Template triển khai thiết kế CTN (Revit)</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>TSK_184</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Cấp thoát nước</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>Hướng dẫn triển khai bản vẽ trên cácTemplate</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr"/>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>TSK_185</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Cấp thoát nước</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>Bộ công cụ tự động hoá kèm danh mục cho hệ thống cấp thoát nước</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>TSK_186</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Cấp thoát nước</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>Tài liệu tập hợp các lỗi hay gặp trong thiết kế CTN các hạng mục</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>TSK_187</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Cấp thoát nước</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>Chuẩn hoá thiết kế các hạng mục</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>TSK_188</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Cấp thoát nước</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>BOQ chuẩn hoá hệ thống cấp thoát nước</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>TSK_189</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Cấp thoát nước</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>Các biểu mẫu so sánh giữa các phương án thiết kế CTN</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>TSK_190</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Phòng cháy chữa cháy</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>Thuyết minh thiết kế hệ thống PCCC, chỉ dẫn kĩ thuật</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>TSK_191</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Phòng cháy chữa cháy</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>Quy định đặt tên file, mã bản vẽ, tên family, tham biến…hệ thống PCCC</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>TSK_192</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Phòng cháy chữa cháy</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>Các bảng tính thiết kế hệ thống PCCC</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>TSK_193</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Phòng cháy chữa cháy</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>Biểu mẫu câu hỏi làm rõ thông tin kĩ thuật đầu vào khi triển khai dự án</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr"/>
-      <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>TSK_194</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Phòng cháy chữa cháy</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>Check list danh mục hồ sơ thông tin đầu vào triển khai phương án thiết kế PCCC dự án</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>TSK_195</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Phòng cháy chữa cháy</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>Danh mục vật tư, thiết bị kèm mã hệ thống PCCC</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>TSK_196</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Phòng cháy chữa cháy</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>Template (Autocad) bao gồm chi tiết lắp đặt điển hình của hệ thống PCCC</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr"/>
-      <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>TSK_197</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Phòng cháy chữa cháy</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>Biểu mẫu lập tiến độ thiết kế hệ thống PCCC</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr"/>
-      <c r="I198" t="inlineStr"/>
-      <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>TSK_198</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Phòng cháy chữa cháy</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>Danh mục bản vẽ (tên và mã) hệ thôgns PCCC</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr"/>
-      <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>TSK_199</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Phòng cháy chữa cháy</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>Quy trình thiết kế tổng thể và chi tiết theo từng hạng mục</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr"/>
-      <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>TSK_200</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Phòng cháy chữa cháy</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>Các sơ đồ nguyên lý điển hình PCCC</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr"/>
-      <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr"/>
-      <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>TSK_201</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Phòng cháy chữa cháy</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>Template triển khai thiết kế PCCC (Revit)</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr"/>
-      <c r="I202" t="inlineStr"/>
-      <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>TSK_202</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Phòng cháy chữa cháy</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>Hướng dẫn triển khai bản vẽ trên cácTemplate PCCC</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr"/>
-      <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>TSK_203</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Phòng cháy chữa cháy</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>Bộ công cụ tự động hoá kèm danh mục hệ thống PCCC</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr"/>
-      <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr"/>
-      <c r="N204" t="inlineStr"/>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>TSK_204</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Phòng cháy chữa cháy</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>Tài liệu tập hợp các lỗi hay gặp trong thiết kế PCCC các hạng mục</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr"/>
-      <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>TSK_205</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Phòng cháy chữa cháy</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>Chuẩn hoá thiết kế các hạng mục hệ PCCC</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr"/>
-      <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>TSK_206</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Phòng cháy chữa cháy</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>BOQ chuẩn hoá hệ PCCC</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr"/>
-      <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr"/>
-      <c r="N207" t="inlineStr"/>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>TSK_207</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa Bộ môn Thiết kế</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Phòng cháy chữa cháy</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>Các biểu mẫu so sánh giữa các phương án thiết kế PCCC</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr"/>
-      <c r="I208" t="inlineStr"/>
-      <c r="J208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>TSK_208</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Quản trị &amp; Tổ chức</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Đào tạo phát triển</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>Đào tạo về quản lý dự án với BIM (khoảng 20 buổi)</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr"/>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>2026-12-30</t>
-        </is>
-      </c>
-      <c r="J209" t="inlineStr"/>
-      <c r="K209" t="inlineStr"/>
-      <c r="L209" t="inlineStr"/>
-      <c r="M209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>TSK_209</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Quản trị &amp; Tổ chức</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Đào tạo phát triển</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>Đào tạo lập trình, sử dụng công cụ tự động hoá</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr"/>
-      <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
-      <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>TSK_210</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Quản trị &amp; Tổ chức</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Đào tạo phát triển</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>Đào tạo tư duy hoạch định mục tiêu, kế hoạch</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>Chưa thực hiện</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr"/>
-      <c r="H211" t="inlineStr"/>
-      <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr"/>
-      <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>TSK_211</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Quản trị &amp; Tổ chức</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Xây dựng văn hoá</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>Truyền thông tinh thần làm việc, văn háo học tập, chia sẻ</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>2024-11-01</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr"/>
-      <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr"/>
-      <c r="N212" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>TSK_212</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Quản trị &amp; Tổ chức</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Xây dựng văn hoá</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>Tổ chức các hoạt động gắn kết đội nhóm</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>2024-11-01</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr"/>
-      <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr"/>
-      <c r="M213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>TSK_213</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Quản trị &amp; Tổ chức</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Xây dựng văn hoá</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>Trợ lực, đồng hành, cầm tay chỉ việc cho các nhiệm vụ khó khăn</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>2024-11-01</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr"/>
-      <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>TSK_214</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Quản trị &amp; Tổ chức</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Xây dựng văn hoá</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>Định hướng phát triển tương lai, đối thoại thẳng thắn, tôn trọng quyết định người lao động</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>Đang thực hiện</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>P. BIM</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>2024-11-01</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr"/>
-      <c r="I215" t="inlineStr"/>
-      <c r="J215" t="inlineStr"/>
-      <c r="K215" t="inlineStr"/>
-      <c r="L215" t="inlineStr"/>
-      <c r="M215" t="inlineStr"/>
-      <c r="N215" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BIM_TK_PowerBI_DataModel_2026.xlsx
+++ b/BIM_TK_PowerBI_DataModel_2026.xlsx
@@ -30565,12 +30565,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
+          <t>Dự Án Mẫu (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -30617,12 +30617,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
+          <t>Dự Án Mẫu (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -30669,12 +30669,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
+          <t>Dự Án Mẫu (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -30721,12 +30721,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
+          <t>Dự Án Mẫu (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -30773,12 +30773,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
+          <t>Dự Án Mẫu (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -30825,12 +30825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
+          <t>Dự Án Mẫu (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -30877,12 +30877,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
+          <t>Dự Án Mẫu (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -30929,12 +30929,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
+          <t>Dự Án Mẫu (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -30981,12 +30981,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
+          <t>Dự Án Mẫu (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -31033,12 +31033,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
+          <t>Dự Án Mẫu (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -31085,12 +31085,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
+          <t>Dự Án Mẫu (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -31137,12 +31137,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
+          <t>Dự Án Mẫu (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -31189,12 +31189,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
+          <t>Dự Án Mẫu (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -31241,12 +31241,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
+          <t>Dự Án Mẫu (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -31293,12 +31293,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
+          <t>Dự Án Mẫu (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
+          <t>Dự Án Mẫu (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -31397,12 +31397,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
+          <t>Dự Án Mẫu (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -31449,12 +31449,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
+          <t>Dự Án Mẫu (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -31501,12 +31501,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
+          <t>Dự Án Mẫu (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -31553,12 +31553,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
+          <t>Dự Án Mẫu (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -31605,12 +31605,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
+          <t>Dự Án Mẫu (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -31657,12 +31657,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
+          <t>Dự Án Mẫu (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -31709,12 +31709,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
+          <t>Dự Án Mẫu (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -31757,12 +31757,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA (Thực chiến triển khai)</t>
+          <t>Dự Án Mẫu (Thực chiến triển khai)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dự Án Mẫu MEGA</t>
+          <t>Dự Án Mẫu</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
